--- a/New_Outputs/lavaan_mediation/Stats_Parallel_Mediation_ROE_receptors_NRS.xlsx
+++ b/New_Outputs/lavaan_mediation/Stats_Parallel_Mediation_ROE_receptors_NRS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="145">
   <si>
     <t>line</t>
   </si>
@@ -360,7 +360,19 @@
     <t>C1</t>
   </si>
   <si>
-    <t>d1</t>
+    <t>dM1_1</t>
+  </si>
+  <si>
+    <t>dM2_1</t>
+  </si>
+  <si>
+    <t>dM3_1</t>
+  </si>
+  <si>
+    <t>dM4_1</t>
+  </si>
+  <si>
+    <t>dY_1</t>
   </si>
   <si>
     <t>p_fmt</t>
@@ -3294,25 +3306,25 @@
         <v>61</v>
       </c>
       <c r="F2">
-        <v>0.3288914021880558</v>
+        <v>0.3032623719217752</v>
       </c>
       <c r="G2">
-        <v>0.1845042611485585</v>
+        <v>0.2631700359454516</v>
       </c>
       <c r="H2">
-        <v>1.782568056372639</v>
+        <v>1.152343848083958</v>
       </c>
       <c r="I2">
-        <v>0.07465664358409518</v>
+        <v>0.2491798053673879</v>
       </c>
       <c r="J2">
-        <v>0.01532865873635998</v>
+        <v>-0.1761772244726907</v>
       </c>
       <c r="K2">
-        <v>0.7474419753273286</v>
+        <v>0.8678966291675029</v>
       </c>
       <c r="L2">
-        <v>0.3281664124532698</v>
+        <v>0.3032623706348011</v>
       </c>
       <c r="M2">
         <v>36</v>
@@ -3335,25 +3347,25 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>0.170897934804169</v>
+        <v>0.1379947800360535</v>
       </c>
       <c r="G3">
-        <v>0.1230470439836724</v>
+        <v>0.2553819712867732</v>
       </c>
       <c r="H3">
-        <v>1.388882896096603</v>
+        <v>0.5403466005871518</v>
       </c>
       <c r="I3">
-        <v>0.1648683623479903</v>
+        <v>0.588958026560046</v>
       </c>
       <c r="J3">
-        <v>-0.06920845095339204</v>
+        <v>-0.4087309186920889</v>
       </c>
       <c r="K3">
-        <v>0.4183096827182238</v>
+        <v>0.6038274893621236</v>
       </c>
       <c r="L3">
-        <v>0.1705212169951754</v>
+        <v>0.1379947794504362</v>
       </c>
       <c r="M3">
         <v>36</v>
@@ -3376,25 +3388,25 @@
         <v>63</v>
       </c>
       <c r="F4">
-        <v>-0.08010479509644436</v>
+        <v>0.05188445384553334</v>
       </c>
       <c r="G4">
-        <v>0.2274480805037279</v>
+        <v>0.314984127341175</v>
       </c>
       <c r="H4">
-        <v>-0.3521893652346361</v>
+        <v>0.1647208520743482</v>
       </c>
       <c r="I4">
-        <v>0.7246962519860145</v>
+        <v>0.8691637035933995</v>
       </c>
       <c r="J4">
-        <v>-0.5240474248411527</v>
+        <v>-0.5360119995427105</v>
       </c>
       <c r="K4">
-        <v>0.3672759399950338</v>
+        <v>0.6850130406089554</v>
       </c>
       <c r="L4">
-        <v>-0.08103298455837164</v>
+        <v>0.05188445416025984</v>
       </c>
       <c r="M4">
         <v>36</v>
@@ -3414,28 +3426,28 @@
         <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5">
-        <v>0.1708979348041691</v>
+        <v>0.3403483007121995</v>
       </c>
       <c r="G5">
-        <v>0.1230470439836724</v>
+        <v>0.2289960080092887</v>
       </c>
       <c r="H5">
-        <v>1.388882896096603</v>
+        <v>1.486263029958121</v>
       </c>
       <c r="I5">
-        <v>0.1648683623479901</v>
+        <v>0.1372095614536664</v>
       </c>
       <c r="J5">
-        <v>-0.06920845095339188</v>
+        <v>-0.1090721259299342</v>
       </c>
       <c r="K5">
-        <v>0.4183096827182239</v>
+        <v>0.796230112381024</v>
       </c>
       <c r="L5">
-        <v>0.1728781616053162</v>
+        <v>0.3403483027767224</v>
       </c>
       <c r="M5">
         <v>36</v>
@@ -3458,25 +3470,25 @@
         <v>65</v>
       </c>
       <c r="F6">
-        <v>0.05375572932430051</v>
+        <v>0.1731056214505613</v>
       </c>
       <c r="G6">
-        <v>0.2403720502623177</v>
+        <v>0.3609806762570069</v>
       </c>
       <c r="H6">
-        <v>0.2236355236211404</v>
+        <v>0.4795426260637716</v>
       </c>
       <c r="I6">
-        <v>0.8230409197958881</v>
+        <v>0.6315526513473615</v>
       </c>
       <c r="J6">
-        <v>-0.4037408590539399</v>
+        <v>-0.5056995764867448</v>
       </c>
       <c r="K6">
-        <v>0.5314480906161949</v>
+        <v>0.8753271451132619</v>
       </c>
       <c r="L6">
-        <v>0.05431801775096259</v>
+        <v>0.1731056209147398</v>
       </c>
       <c r="M6">
         <v>36</v>
@@ -3496,28 +3508,28 @@
         <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F7">
-        <v>0.170897934804169</v>
+        <v>0.3241216753335413</v>
       </c>
       <c r="G7">
-        <v>0.1230470439836724</v>
+        <v>0.2729230625395496</v>
       </c>
       <c r="H7">
-        <v>1.388882896096603</v>
+        <v>1.187593574238793</v>
       </c>
       <c r="I7">
-        <v>0.1648683623479903</v>
+        <v>0.2349935706599982</v>
       </c>
       <c r="J7">
-        <v>-0.06920845095339197</v>
+        <v>-0.2011965589232184</v>
       </c>
       <c r="K7">
-        <v>0.4183096827182238</v>
+        <v>0.86902088349373</v>
       </c>
       <c r="L7">
-        <v>0.1726855383226911</v>
+        <v>0.3241216743302733</v>
       </c>
       <c r="M7">
         <v>36</v>
@@ -3540,25 +3552,25 @@
         <v>67</v>
       </c>
       <c r="F8">
-        <v>0.4064616178535701</v>
+        <v>-0.001213102105891759</v>
       </c>
       <c r="G8">
-        <v>0.1679534680617492</v>
+        <v>0.2348873363670402</v>
       </c>
       <c r="H8">
-        <v>2.42008469693601</v>
+        <v>-0.005164612637933526</v>
       </c>
       <c r="I8">
-        <v>0.01551689248523336</v>
+        <v>0.9958792536326053</v>
       </c>
       <c r="J8">
-        <v>0.1295382704210442</v>
+        <v>-0.4682025060634204</v>
       </c>
       <c r="K8">
-        <v>0.7957887275025883</v>
+        <v>0.445362569140955</v>
       </c>
       <c r="L8">
-        <v>0.3928764619395423</v>
+        <v>-0.001213102114597608</v>
       </c>
       <c r="M8">
         <v>36</v>
@@ -3578,28 +3590,28 @@
         <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F9">
-        <v>0.170897934804169</v>
+        <v>-0.3524832028006372</v>
       </c>
       <c r="G9">
-        <v>0.1230470439836724</v>
+        <v>0.2693138759056411</v>
       </c>
       <c r="H9">
-        <v>1.388882896096602</v>
+        <v>-1.3088193158088</v>
       </c>
       <c r="I9">
-        <v>0.1648683623479903</v>
+        <v>0.1905955623590889</v>
       </c>
       <c r="J9">
-        <v>-0.06920845095339218</v>
+        <v>-0.8971459746756018</v>
       </c>
       <c r="K9">
-        <v>0.4183096827182238</v>
+        <v>0.1503253976712387</v>
       </c>
       <c r="L9">
-        <v>0.1651860176446591</v>
+        <v>-0.3524832053302394</v>
       </c>
       <c r="M9">
         <v>36</v>
@@ -3622,25 +3634,25 @@
         <v>69</v>
       </c>
       <c r="F10">
-        <v>0.2974517415577763</v>
+        <v>0.3040259186483687</v>
       </c>
       <c r="G10">
-        <v>0.1890629237528517</v>
+        <v>0.2866541318793874</v>
       </c>
       <c r="H10">
-        <v>1.57329494145882</v>
+        <v>1.060601906049939</v>
       </c>
       <c r="I10">
-        <v>0.1156505401133909</v>
+        <v>0.2888708559846507</v>
       </c>
       <c r="J10">
-        <v>-0.1551365656897017</v>
+        <v>-0.3605092390815969</v>
       </c>
       <c r="K10">
-        <v>0.6154665692995134</v>
+        <v>0.7684928986254855</v>
       </c>
       <c r="L10">
-        <v>0.2932295709812802</v>
+        <v>0.3040259194592988</v>
       </c>
       <c r="M10">
         <v>36</v>
@@ -3663,25 +3675,25 @@
         <v>70</v>
       </c>
       <c r="F11">
-        <v>-0.3363896379222368</v>
+        <v>-0.337775511713833</v>
       </c>
       <c r="G11">
-        <v>0.1852202905944938</v>
+        <v>0.1962917397268776</v>
       </c>
       <c r="H11">
-        <v>-1.816159756809262</v>
+        <v>-1.720783116924928</v>
       </c>
       <c r="I11">
-        <v>0.06934586930839748</v>
+        <v>0.08529018716125103</v>
       </c>
       <c r="J11">
-        <v>-0.7277969579377647</v>
+        <v>-0.7491897117662188</v>
       </c>
       <c r="K11">
-        <v>-0.003764206007551322</v>
+        <v>0.0214821613523745</v>
       </c>
       <c r="L11">
-        <v>-0.3323473723264181</v>
+        <v>-0.3377755140482234</v>
       </c>
       <c r="M11">
         <v>36</v>
@@ -3704,25 +3716,25 @@
         <v>71</v>
       </c>
       <c r="F12">
-        <v>0.05683545820742896</v>
+        <v>0.05580207620268011</v>
       </c>
       <c r="G12">
-        <v>0.1630161188248445</v>
+        <v>0.1761413225872891</v>
       </c>
       <c r="H12">
-        <v>0.3486493152772016</v>
+        <v>0.3168028681914016</v>
       </c>
       <c r="I12">
-        <v>0.7273525997854193</v>
+        <v>0.7513931877291673</v>
       </c>
       <c r="J12">
-        <v>-0.2503626701598362</v>
+        <v>-0.2702414116657186</v>
       </c>
       <c r="K12">
-        <v>0.3841989360033988</v>
+        <v>0.4199865404937983</v>
       </c>
       <c r="L12">
-        <v>0.05538692998848272</v>
+        <v>0.05580207601303086</v>
       </c>
       <c r="M12">
         <v>36</v>
@@ -3745,25 +3757,25 @@
         <v>72</v>
       </c>
       <c r="F13">
-        <v>0.1802889828323825</v>
+        <v>0.1784192569386154</v>
       </c>
       <c r="G13">
-        <v>0.1775363187172182</v>
+        <v>0.1809081601837636</v>
       </c>
       <c r="H13">
-        <v>1.015504794371391</v>
+        <v>0.9862421725884556</v>
       </c>
       <c r="I13">
-        <v>0.3098652623195737</v>
+        <v>0.3240142890373685</v>
       </c>
       <c r="J13">
-        <v>-0.2062910520429322</v>
+        <v>-0.2006791689329991</v>
       </c>
       <c r="K13">
-        <v>0.5027347847380091</v>
+        <v>0.5213406208161808</v>
       </c>
       <c r="L13">
-        <v>0.17589005440256</v>
+        <v>0.1784192579667831</v>
       </c>
       <c r="M13">
         <v>36</v>
@@ -3786,25 +3798,25 @@
         <v>73</v>
       </c>
       <c r="F14">
-        <v>0.416155616208209</v>
+        <v>0.4182570101210575</v>
       </c>
       <c r="G14">
-        <v>0.1912829990583168</v>
+        <v>0.2031388676682258</v>
       </c>
       <c r="H14">
-        <v>2.175601690986322</v>
+        <v>2.058970865212121</v>
       </c>
       <c r="I14">
-        <v>0.02958505679588552</v>
+        <v>0.03949702957415435</v>
       </c>
       <c r="J14">
-        <v>0.03213637654339146</v>
+        <v>0.01261489650859279</v>
       </c>
       <c r="K14">
-        <v>0.7987306705205643</v>
+        <v>0.8318209779059474</v>
       </c>
       <c r="L14">
-        <v>0.4244343653207523</v>
+        <v>0.418257008235048</v>
       </c>
       <c r="M14">
         <v>36</v>
@@ -3824,28 +3836,28 @@
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F15">
-        <v>0.170897934804169</v>
+        <v>0.1802004184875507</v>
       </c>
       <c r="G15">
-        <v>0.1230470439836724</v>
+        <v>0.2826088094856761</v>
       </c>
       <c r="H15">
-        <v>1.388882896096603</v>
+        <v>0.6376319931975936</v>
       </c>
       <c r="I15">
-        <v>0.1648683623479903</v>
+        <v>0.5237132644143143</v>
       </c>
       <c r="J15">
-        <v>-0.06920845095339204</v>
+        <v>-0.3979528944355643</v>
       </c>
       <c r="K15">
-        <v>0.4183096827182238</v>
+        <v>0.7451123796750988</v>
       </c>
       <c r="L15">
-        <v>0.1684721287620352</v>
+        <v>0.1802004189682004</v>
       </c>
       <c r="M15">
         <v>36</v>
@@ -3865,25 +3877,25 @@
         <v>62</v>
       </c>
       <c r="F16">
-        <v>-0.1864330212757695</v>
+        <v>-0.1843012964449261</v>
       </c>
       <c r="G16">
-        <v>0.1329226353996138</v>
+        <v>0.1316641768416178</v>
       </c>
       <c r="H16">
-        <v>-1.402567897599112</v>
+        <v>-1.399783151848713</v>
       </c>
       <c r="I16">
-        <v>0.1607457303010247</v>
+        <v>0.1615782645731845</v>
       </c>
       <c r="J16">
-        <v>-0.4502739470226804</v>
+        <v>-0.4411336608925669</v>
       </c>
       <c r="K16">
-        <v>0.07337318276510765</v>
+        <v>0.07416283281113555</v>
       </c>
       <c r="L16">
-        <v>-0.2045908048754095</v>
+        <v>-0.2035492952400708</v>
       </c>
       <c r="M16">
         <v>36</v>
@@ -3903,25 +3915,25 @@
         <v>64</v>
       </c>
       <c r="F17">
-        <v>-0.06162455095361027</v>
+        <v>-0.05969688878517659</v>
       </c>
       <c r="G17">
-        <v>0.1694691961222847</v>
+        <v>0.1648272140717967</v>
       </c>
       <c r="H17">
-        <v>-0.3636327566523862</v>
+        <v>-0.3621785948476529</v>
       </c>
       <c r="I17">
-        <v>0.7161322626898423</v>
+        <v>0.7172185741341308</v>
       </c>
       <c r="J17">
-        <v>-0.388143998216585</v>
+        <v>-0.3737570348176256</v>
       </c>
       <c r="K17">
-        <v>0.2795405341340598</v>
+        <v>0.2716175755775743</v>
       </c>
       <c r="L17">
-        <v>-0.06615668537576558</v>
+        <v>-0.06441153993340383</v>
       </c>
       <c r="M17">
         <v>36</v>
@@ -3941,25 +3953,25 @@
         <v>66</v>
       </c>
       <c r="F18">
-        <v>0.2884997907223294</v>
+        <v>0.2819150239530773</v>
       </c>
       <c r="G18">
-        <v>0.1347103912531575</v>
+        <v>0.121923110967538</v>
       </c>
       <c r="H18">
-        <v>2.141629818149364</v>
+        <v>2.31223614387708</v>
       </c>
       <c r="I18">
-        <v>0.03222328230280436</v>
+        <v>0.02076467348687472</v>
       </c>
       <c r="J18">
-        <v>0.01408626749239384</v>
+        <v>0.0208630032730615</v>
       </c>
       <c r="K18">
-        <v>0.5425379333897646</v>
+        <v>0.4965322419512202</v>
       </c>
       <c r="L18">
-        <v>0.3061515932263879</v>
+        <v>0.3170885655399893</v>
       </c>
       <c r="M18">
         <v>36</v>
@@ -3979,25 +3991,25 @@
         <v>64</v>
       </c>
       <c r="F19">
-        <v>-0.04317538931411881</v>
+        <v>-0.05310272364602901</v>
       </c>
       <c r="G19">
-        <v>0.1478141784137358</v>
+        <v>0.1483594949713934</v>
       </c>
       <c r="H19">
-        <v>-0.2920923403793494</v>
+        <v>-0.3579327609349726</v>
       </c>
       <c r="I19">
-        <v>0.7702160229434314</v>
+        <v>0.7203936330690226</v>
       </c>
       <c r="J19">
-        <v>-0.3418118038965627</v>
+        <v>-0.3448435436500421</v>
       </c>
       <c r="K19">
-        <v>0.2291022092971302</v>
+        <v>0.2381619707239643</v>
       </c>
       <c r="L19">
-        <v>-0.04720747913929899</v>
+        <v>-0.05870395098821798</v>
       </c>
       <c r="M19">
         <v>36</v>
@@ -4017,25 +4029,25 @@
         <v>66</v>
       </c>
       <c r="F20">
-        <v>-0.2271645377853858</v>
+        <v>-0.1932549987353026</v>
       </c>
       <c r="G20">
-        <v>0.1278893723072676</v>
+        <v>0.1101521598848542</v>
       </c>
       <c r="H20">
-        <v>-1.776258133784559</v>
+        <v>-1.754436762178051</v>
       </c>
       <c r="I20">
-        <v>0.07569038035289832</v>
+        <v>0.07935569678195509</v>
       </c>
       <c r="J20">
-        <v>-0.4785024076872439</v>
+        <v>-0.3890140508617886</v>
       </c>
       <c r="K20">
-        <v>0.02908902193258588</v>
+        <v>0.03618296233374526</v>
       </c>
       <c r="L20">
-        <v>-0.2455195810467591</v>
+        <v>-0.2227058611557943</v>
       </c>
       <c r="M20">
         <v>36</v>
@@ -4055,25 +4067,25 @@
         <v>66</v>
       </c>
       <c r="F21">
-        <v>0.2905225848199399</v>
+        <v>0.3211851693178581</v>
       </c>
       <c r="G21">
-        <v>0.139271904966334</v>
+        <v>0.1241261925524224</v>
       </c>
       <c r="H21">
-        <v>2.086009988088894</v>
+        <v>2.587569655632605</v>
       </c>
       <c r="I21">
-        <v>0.03697771832087948</v>
+        <v>0.009665565125861919</v>
       </c>
       <c r="J21">
-        <v>0.01236089985203664</v>
+        <v>0.05889303387819284</v>
       </c>
       <c r="K21">
-        <v>0.5575935858525771</v>
+        <v>0.5476803427256073</v>
       </c>
       <c r="L21">
-        <v>0.307172403044119</v>
+        <v>0.3615989544845027</v>
       </c>
       <c r="M21">
         <v>36</v>
@@ -4093,25 +4105,25 @@
         <v>112</v>
       </c>
       <c r="F22">
-        <v>-0.757288161078542</v>
+        <v>-0.7572881932320493</v>
       </c>
       <c r="G22">
-        <v>0.1029197534921611</v>
+        <v>0.1029208282252121</v>
       </c>
       <c r="H22">
-        <v>-7.358044839625669</v>
+        <v>-7.357968316917792</v>
       </c>
       <c r="I22">
-        <v>1.865174681370263E-13</v>
+        <v>1.867395127419513E-13</v>
       </c>
       <c r="J22">
-        <v>-0.9451532984324977</v>
+        <v>-0.9451812892714206</v>
       </c>
       <c r="K22">
-        <v>-0.5508839467138862</v>
+        <v>-0.5508607075589825</v>
       </c>
       <c r="L22">
-        <v>-0.7789249527987545</v>
+        <v>-0.7789249987529647</v>
       </c>
       <c r="M22">
         <v>36</v>
@@ -4134,25 +4146,25 @@
         <v>78</v>
       </c>
       <c r="F23">
-        <v>-0.1106356596977769</v>
+        <v>-0.1024346028594284</v>
       </c>
       <c r="G23">
-        <v>0.1014095010733834</v>
+        <v>0.1208271257268132</v>
       </c>
       <c r="H23">
-        <v>-1.090979232978546</v>
+        <v>-0.8477781975136131</v>
       </c>
       <c r="I23">
-        <v>0.2752820206281539</v>
+        <v>0.3965615073940287</v>
       </c>
       <c r="J23">
-        <v>-0.3797592427206687</v>
+        <v>-0.4157216898743987</v>
       </c>
       <c r="K23">
-        <v>0.009724422256596681</v>
+        <v>0.0495474335167362</v>
       </c>
       <c r="L23">
-        <v>-0.1090652448646317</v>
+        <v>-0.1024346031326528</v>
       </c>
       <c r="M23">
         <v>36</v>
@@ -4175,25 +4187,25 @@
         <v>81</v>
       </c>
       <c r="F24">
-        <v>-0.004552792733918624</v>
+        <v>0.002895260247222891</v>
       </c>
       <c r="G24">
-        <v>0.04454032148809441</v>
+        <v>0.06615501074717887</v>
       </c>
       <c r="H24">
-        <v>-0.1022173298667272</v>
+        <v>0.04376479142732747</v>
       </c>
       <c r="I24">
-        <v>0.9185841725591373</v>
+        <v>0.9650918925500762</v>
       </c>
       <c r="J24">
-        <v>-0.1059504229334995</v>
+        <v>-0.1195538222047855</v>
       </c>
       <c r="K24">
-        <v>0.08083057627694527</v>
+        <v>0.162731656565618</v>
       </c>
       <c r="L24">
-        <v>-0.004488168242492332</v>
+        <v>0.002895260254945435</v>
       </c>
       <c r="M24">
         <v>36</v>
@@ -4216,25 +4228,25 @@
         <v>84</v>
       </c>
       <c r="F25">
-        <v>0.009691565761291012</v>
+        <v>0.03088537635110638</v>
       </c>
       <c r="G25">
-        <v>0.05723377977477266</v>
+        <v>0.0932612547100491</v>
       </c>
       <c r="H25">
-        <v>0.1693329673390334</v>
+        <v>0.3311704999801854</v>
       </c>
       <c r="I25">
-        <v>0.8655347462059979</v>
+        <v>0.7405157017422508</v>
       </c>
       <c r="J25">
-        <v>-0.08301217553604819</v>
+        <v>-0.1237910610254593</v>
       </c>
       <c r="K25">
-        <v>0.1582315353378403</v>
+        <v>0.2685277764934617</v>
       </c>
       <c r="L25">
-        <v>0.00955399909725603</v>
+        <v>0.03088537643348712</v>
       </c>
       <c r="M25">
         <v>36</v>
@@ -4257,25 +4269,25 @@
         <v>87</v>
       </c>
       <c r="F26">
-        <v>0.169151285042838</v>
+        <v>-0.0005073884597818456</v>
       </c>
       <c r="G26">
-        <v>0.1204023640681945</v>
+        <v>0.1075237010252772</v>
       </c>
       <c r="H26">
-        <v>1.404883420287601</v>
+        <v>-0.004718852261814965</v>
       </c>
       <c r="I26">
-        <v>0.1600559475283825</v>
+        <v>0.9962349146088083</v>
       </c>
       <c r="J26">
-        <v>0.006489833791271483</v>
+        <v>-0.2169194856811365</v>
       </c>
       <c r="K26">
-        <v>0.4591523183225297</v>
+        <v>0.2291588785226428</v>
       </c>
       <c r="L26">
-        <v>0.1667502717727724</v>
+        <v>-0.0005073884611352059</v>
       </c>
       <c r="M26">
         <v>36</v>
@@ -4298,25 +4310,25 @@
         <v>88</v>
       </c>
       <c r="F27">
-        <v>0.06365439837243354</v>
+        <v>-0.06916135472088095</v>
       </c>
       <c r="G27">
-        <v>0.141021919103793</v>
+        <v>0.1850329423817499</v>
       </c>
       <c r="H27">
-        <v>0.451379464816271</v>
+        <v>-0.3737786030456728</v>
       </c>
       <c r="I27">
-        <v>0.6517160810320202</v>
+        <v>0.7085690398450974</v>
       </c>
       <c r="J27">
-        <v>-0.1895833465470553</v>
+        <v>-0.4481453697910466</v>
       </c>
       <c r="K27">
-        <v>0.3723940436578909</v>
+        <v>0.2867003363101536</v>
       </c>
       <c r="L27">
-        <v>0.06275085776290433</v>
+        <v>-0.06916135490535542</v>
       </c>
       <c r="M27">
         <v>36</v>
@@ -4339,25 +4351,25 @@
         <v>90</v>
       </c>
       <c r="F28">
-        <v>0.3611061399302098</v>
+        <v>0.2348645639274878</v>
       </c>
       <c r="G28">
-        <v>0.2087451591839281</v>
+        <v>0.3169399567841402</v>
       </c>
       <c r="H28">
-        <v>1.729889887468167</v>
+        <v>0.7410380385943199</v>
       </c>
       <c r="I28">
-        <v>0.08364995038379219</v>
+        <v>0.458670376722278</v>
       </c>
       <c r="J28">
-        <v>-0.06144693289275445</v>
+        <v>-0.4646755585646112</v>
       </c>
       <c r="K28">
-        <v>0.7622039010075838</v>
+        <v>0.7867021128651055</v>
       </c>
       <c r="L28">
-        <v>0.3559804287441846</v>
+        <v>0.2348645645539434</v>
       </c>
       <c r="M28">
         <v>36</v>
@@ -4380,25 +4392,25 @@
         <v>94</v>
       </c>
       <c r="F29">
-        <v>-0.1060828669638583</v>
+        <v>-0.1053298631066513</v>
       </c>
       <c r="G29">
-        <v>0.1156246183165462</v>
+        <v>0.1377877619800272</v>
       </c>
       <c r="H29">
-        <v>-0.9174764726438668</v>
+        <v>-0.7644355463289926</v>
       </c>
       <c r="I29">
-        <v>0.3588930160772015</v>
+        <v>0.4446077325532496</v>
       </c>
       <c r="J29">
-        <v>-0.3960283978776726</v>
+        <v>-0.4376924601224617</v>
       </c>
       <c r="K29">
-        <v>0.06838640965984528</v>
+        <v>0.10394963329537</v>
       </c>
       <c r="L29">
-        <v>-0.1045770766221394</v>
+        <v>-0.1053298633875982</v>
       </c>
       <c r="M29">
         <v>36</v>
@@ -4421,25 +4433,25 @@
         <v>97</v>
       </c>
       <c r="F30">
-        <v>-0.1203272254590679</v>
+        <v>-0.1333199792105348</v>
       </c>
       <c r="G30">
-        <v>0.1154632869134265</v>
+        <v>0.1365856211965054</v>
       </c>
       <c r="H30">
-        <v>-1.042125412117259</v>
+        <v>-0.9760908801573456</v>
       </c>
       <c r="I30">
-        <v>0.2973535382111328</v>
+        <v>0.3290194303236502</v>
       </c>
       <c r="J30">
-        <v>-0.4190837374347809</v>
+        <v>-0.4664394305478671</v>
       </c>
       <c r="K30">
-        <v>0.04934560697882039</v>
+        <v>0.08278392531226027</v>
       </c>
       <c r="L30">
-        <v>-0.1186192439618878</v>
+        <v>-0.1333199795661399</v>
       </c>
       <c r="M30">
         <v>36</v>
@@ -4462,25 +4474,25 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>-0.2797869447406149</v>
+        <v>-0.1019272143996465</v>
       </c>
       <c r="G31">
-        <v>0.18767993755336</v>
+        <v>0.185840403962908</v>
       </c>
       <c r="H31">
-        <v>-1.490766399371097</v>
+        <v>-0.5484663841991554</v>
       </c>
       <c r="I31">
-        <v>0.1360228363237499</v>
+        <v>0.5833717051464871</v>
       </c>
       <c r="J31">
-        <v>-0.7517936994050185</v>
+        <v>-0.5458432890825459</v>
       </c>
       <c r="K31">
-        <v>-0.02896210274054355</v>
+        <v>0.1980592230770578</v>
       </c>
       <c r="L31">
-        <v>-0.2758155166374041</v>
+        <v>-0.1019272146715176</v>
       </c>
       <c r="M31">
         <v>36</v>
@@ -4503,25 +4515,25 @@
         <v>103</v>
       </c>
       <c r="F32">
-        <v>-0.01424435849520964</v>
+        <v>-0.02799011610388349</v>
       </c>
       <c r="G32">
-        <v>0.07364873725339015</v>
+        <v>0.1181422609092905</v>
       </c>
       <c r="H32">
-        <v>-0.1934094055978393</v>
+        <v>-0.2369187443041595</v>
       </c>
       <c r="I32">
-        <v>0.8466383499045946</v>
+        <v>0.8127198280670509</v>
       </c>
       <c r="J32">
-        <v>-0.1911842912477185</v>
+        <v>-0.2907239360894323</v>
       </c>
       <c r="K32">
-        <v>0.1140176191256084</v>
+        <v>0.2151074556709852</v>
       </c>
       <c r="L32">
-        <v>-0.01404216733974836</v>
+        <v>-0.02799011617854169</v>
       </c>
       <c r="M32">
         <v>36</v>
@@ -4544,25 +4556,25 @@
         <v>106</v>
       </c>
       <c r="F33">
-        <v>-0.1737040777767566</v>
+        <v>0.003402648707004736</v>
       </c>
       <c r="G33">
-        <v>0.1278820551406857</v>
+        <v>0.1332485513865822</v>
       </c>
       <c r="H33">
-        <v>-1.358314718868579</v>
+        <v>0.02553610280634822</v>
       </c>
       <c r="I33">
-        <v>0.1743638417804991</v>
+        <v>0.9796273519937859</v>
       </c>
       <c r="J33">
-        <v>-0.4734281876038082</v>
+        <v>-0.2673562656654493</v>
       </c>
       <c r="K33">
-        <v>0.01088681794174408</v>
+        <v>0.2800695484506508</v>
       </c>
       <c r="L33">
-        <v>-0.1712384400152647</v>
+        <v>0.003402648716080641</v>
       </c>
       <c r="M33">
         <v>36</v>
@@ -4585,25 +4597,25 @@
         <v>109</v>
       </c>
       <c r="F34">
-        <v>-0.159459719281547</v>
+        <v>0.03139276481088823</v>
       </c>
       <c r="G34">
-        <v>0.1287281155282597</v>
+        <v>0.1371533289515304</v>
       </c>
       <c r="H34">
-        <v>-1.238732646921571</v>
+        <v>0.2288880995515781</v>
       </c>
       <c r="I34">
-        <v>0.2154445242149072</v>
+        <v>0.8189558902435499</v>
       </c>
       <c r="J34">
-        <v>-0.4470170869916743</v>
+        <v>-0.2353100674028455</v>
       </c>
       <c r="K34">
-        <v>0.06576581009448877</v>
+        <v>0.3287314775261821</v>
       </c>
       <c r="L34">
-        <v>-0.1571962726755163</v>
+        <v>0.03139276489462233</v>
       </c>
       <c r="M34">
         <v>36</v>
@@ -4639,12 +4651,12 @@
         <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>-0.0167082426418953</v>
@@ -4662,12 +4674,12 @@
         <v>0.8838138305933807</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B3">
         <v>-0.0007874806728245196</v>
@@ -4685,12 +4697,12 @@
         <v>0.9935261493724472</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <v>0.06269613150968362</v>
@@ -4708,12 +4720,12 @@
         <v>0.7842241874788201</v>
       </c>
       <c r="G4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B5">
         <v>-0.01444555127856032</v>
@@ -4731,12 +4743,12 @@
         <v>0.8610994190913419</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B6">
         <v>-0.2002889617983713</v>
@@ -4754,12 +4766,12 @@
         <v>0.5412477521695696</v>
       </c>
       <c r="G6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B7">
         <v>-0.002814924304480512</v>
@@ -4777,12 +4789,12 @@
         <v>0.9870691554941227</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B8">
         <v>-0.04899746773819537</v>
@@ -4800,12 +4812,12 @@
         <v>0.813885054960191</v>
       </c>
       <c r="G8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B9">
         <v>0.4336599635394644</v>
@@ -4823,12 +4835,12 @@
         <v>0.494872484154985</v>
       </c>
       <c r="G9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10">
         <v>0.183580719156476</v>
@@ -4846,12 +4858,12 @@
         <v>0.5983070547963201</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B11">
         <v>0.002027443631655993</v>
@@ -4869,12 +4881,12 @@
         <v>0.9918432578211416</v>
       </c>
       <c r="G11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B12">
         <v>0.111693599247879</v>
@@ -4892,12 +4904,12 @@
         <v>0.7198673614117492</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B13">
         <v>-0.4481055148180247</v>
@@ -4915,12 +4927,12 @@
         <v>0.4836332689499183</v>
       </c>
       <c r="G13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B14">
         <v>1.937644946084428</v>
@@ -4938,7 +4950,7 @@
         <v>0.003748394730827442</v>
       </c>
       <c r="G14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/lavaan_mediation/Stats_Parallel_Mediation_ROE_receptors_NRS.xlsx
+++ b/New_Outputs/lavaan_mediation/Stats_Parallel_Mediation_ROE_receptors_NRS.xlsx
@@ -381,79 +381,79 @@
     <t>ind_MOR activity_g1</t>
   </si>
   <si>
-    <t>0.884</t>
+    <t>0.601</t>
   </si>
   <si>
     <t>ind_5-HT1A activity_g1</t>
   </si>
   <si>
-    <t>0.994</t>
+    <t>0.818</t>
   </si>
   <si>
     <t>ind_5-HT4 activity_g1</t>
   </si>
   <si>
-    <t>0.784</t>
+    <t>0.687</t>
   </si>
   <si>
     <t>ind_5-HT6 activity_g1</t>
   </si>
   <si>
-    <t>0.861</t>
+    <t>0.975</t>
   </si>
   <si>
     <t>ind_MOR activity_g2</t>
   </si>
   <si>
-    <t>0.541</t>
+    <t>0.472</t>
   </si>
   <si>
     <t>ind_5-HT1A activity_g2</t>
   </si>
   <si>
-    <t>0.987</t>
+    <t>0.850</t>
   </si>
   <si>
     <t>ind_5-HT4 activity_g2</t>
   </si>
   <si>
-    <t>0.814</t>
+    <t>0.731</t>
   </si>
   <si>
     <t>ind_5-HT6 activity_g2</t>
   </si>
   <si>
-    <t>0.495</t>
+    <t>0.683</t>
   </si>
   <si>
     <t>diff_ind_MOR activity</t>
   </si>
   <si>
-    <t>0.598</t>
+    <t>0.848</t>
   </si>
   <si>
     <t>diff_ind_5-HT1A activity</t>
   </si>
   <si>
-    <t>0.992</t>
+    <t>0.782</t>
   </si>
   <si>
     <t>diff_ind_5-HT4 activity</t>
   </si>
   <si>
-    <t>0.720</t>
+    <t>0.596</t>
   </si>
   <si>
     <t>diff_ind_5-HT6 activity</t>
   </si>
   <si>
-    <t>0.484</t>
+    <t>0.691</t>
   </si>
   <si>
     <t>diff_cprime</t>
   </si>
   <si>
-    <t>0.004</t>
+    <t>0.793</t>
   </si>
 </sst>
 </file>
@@ -1077,28 +1077,28 @@
         <v>61</v>
       </c>
       <c r="F2">
-        <v>0.1282776791982927</v>
+        <v>0.3978053951395698</v>
       </c>
       <c r="G2">
-        <v>0.2408807813856775</v>
+        <v>0.2161349488266004</v>
       </c>
       <c r="H2">
-        <v>0.5325359643071963</v>
+        <v>1.840541741626057</v>
       </c>
       <c r="I2">
-        <v>0.5943548398215088</v>
+        <v>0.06568874189747653</v>
       </c>
       <c r="J2">
-        <v>-0.3090416449781238</v>
+        <v>0.008836142717704488</v>
       </c>
       <c r="K2">
-        <v>0.6386842967886178</v>
+        <v>0.8514342906835298</v>
       </c>
       <c r="L2">
-        <v>0.1282776793014968</v>
+        <v>0.3978053945132817</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1118,28 +1118,28 @@
         <v>63</v>
       </c>
       <c r="F3">
-        <v>0.05620973326023192</v>
+        <v>-0.1789851784738657</v>
       </c>
       <c r="G3">
-        <v>0.2901606184390844</v>
+        <v>0.2489761838609572</v>
       </c>
       <c r="H3">
-        <v>0.1937193736441958</v>
+        <v>-0.7188847370791959</v>
       </c>
       <c r="I3">
-        <v>0.8463956212254196</v>
+        <v>0.4722119413761356</v>
       </c>
       <c r="J3">
-        <v>-0.4710795769975491</v>
+        <v>-0.6057832048851053</v>
       </c>
       <c r="K3">
-        <v>0.6640891341026558</v>
+        <v>0.3497838002979233</v>
       </c>
       <c r="L3">
-        <v>0.05620973314507936</v>
+        <v>-0.1789851796565996</v>
       </c>
       <c r="M3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1159,28 +1159,28 @@
         <v>65</v>
       </c>
       <c r="F4">
-        <v>0.1072622495058441</v>
+        <v>0.1167132846248925</v>
       </c>
       <c r="G4">
-        <v>0.331047581539151</v>
+        <v>0.2449713909167756</v>
       </c>
       <c r="H4">
-        <v>0.3240085579454954</v>
+        <v>0.4764363878904687</v>
       </c>
       <c r="I4">
-        <v>0.7459315551451642</v>
+        <v>0.6337635161585322</v>
       </c>
       <c r="J4">
-        <v>-0.5119560823873577</v>
+        <v>-0.3130781909576938</v>
       </c>
       <c r="K4">
-        <v>0.7704604107197234</v>
+        <v>0.6291089780550708</v>
       </c>
       <c r="L4">
-        <v>0.1072622480857716</v>
+        <v>0.1167132849069579</v>
       </c>
       <c r="M4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1200,28 +1200,28 @@
         <v>67</v>
       </c>
       <c r="F5">
-        <v>-0.08894236834956057</v>
+        <v>-0.03499378396413864</v>
       </c>
       <c r="G5">
-        <v>0.1970738180608034</v>
+        <v>0.2204444250851292</v>
       </c>
       <c r="H5">
-        <v>-0.4513149906200075</v>
+        <v>-0.158741977487637</v>
       </c>
       <c r="I5">
-        <v>0.6517625421863666</v>
+        <v>0.8738721642289866</v>
       </c>
       <c r="J5">
-        <v>-0.5145526033913927</v>
+        <v>-0.427681605135023</v>
       </c>
       <c r="K5">
-        <v>0.246216725535946</v>
+        <v>0.4183021236005512</v>
       </c>
       <c r="L5">
-        <v>-0.08894236871885981</v>
+        <v>-0.03499378387637474</v>
       </c>
       <c r="M5">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1241,28 +1241,28 @@
         <v>69</v>
       </c>
       <c r="F6">
-        <v>0.4438562181231055</v>
+        <v>0.1742738813614198</v>
       </c>
       <c r="G6">
-        <v>0.236468170056214</v>
+        <v>0.2735502728729877</v>
       </c>
       <c r="H6">
-        <v>1.877023102168848</v>
+        <v>0.6370817310145293</v>
       </c>
       <c r="I6">
-        <v>0.06051492760961952</v>
+        <v>0.5240716077683132</v>
       </c>
       <c r="J6">
-        <v>0.03385973432181697</v>
+        <v>-0.2445787461302188</v>
       </c>
       <c r="K6">
-        <v>0.9597239275376276</v>
+        <v>0.8758543604146419</v>
       </c>
       <c r="L6">
-        <v>0.4438562163489833</v>
+        <v>0.1742738814184243</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1282,28 +1282,28 @@
         <v>70</v>
       </c>
       <c r="F7">
-        <v>-0.1075410853961282</v>
+        <v>-0.2254102469251363</v>
       </c>
       <c r="G7">
-        <v>0.3225201399717184</v>
+        <v>0.332834832580569</v>
       </c>
       <c r="H7">
-        <v>-0.3334399067467799</v>
+        <v>-0.6772435600488765</v>
       </c>
       <c r="I7">
-        <v>0.7388022437549167</v>
+        <v>0.4982514341076683</v>
       </c>
       <c r="J7">
-        <v>-0.8036568524608361</v>
+        <v>-0.9570023584847728</v>
       </c>
       <c r="K7">
-        <v>0.3897411759630897</v>
+        <v>0.3872998687460757</v>
       </c>
       <c r="L7">
-        <v>-0.1075410848797587</v>
+        <v>-0.2254102473537437</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1323,28 +1323,28 @@
         <v>71</v>
       </c>
       <c r="F8">
-        <v>-0.01156705836594711</v>
+        <v>-0.1214446205877575</v>
       </c>
       <c r="G8">
-        <v>0.249008340268459</v>
+        <v>0.2313425138998844</v>
       </c>
       <c r="H8">
-        <v>-0.04645249373364974</v>
+        <v>-0.5249559129469552</v>
       </c>
       <c r="I8">
-        <v>0.9629495976887807</v>
+        <v>0.5996138391356882</v>
       </c>
       <c r="J8">
-        <v>-0.4685738679943936</v>
+        <v>-0.5979658396355831</v>
       </c>
       <c r="K8">
-        <v>0.4777593253444389</v>
+        <v>0.3213572366457855</v>
       </c>
       <c r="L8">
-        <v>-0.01156705834340937</v>
+        <v>-0.1214446198249757</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1364,28 +1364,28 @@
         <v>72</v>
       </c>
       <c r="F9">
-        <v>0.4826013930755747</v>
+        <v>0.4605939846762097</v>
       </c>
       <c r="G9">
-        <v>0.3011845279103721</v>
+        <v>0.265173997939407</v>
       </c>
       <c r="H9">
-        <v>1.602344570698497</v>
+        <v>1.736950033771624</v>
       </c>
       <c r="I9">
-        <v>0.1090794347508754</v>
+        <v>0.08239599080832583</v>
       </c>
       <c r="J9">
-        <v>-0.1215648011207634</v>
+        <v>-0.09907846991981215</v>
       </c>
       <c r="K9">
-        <v>1.036334248086783</v>
+        <v>0.9550785356671507</v>
       </c>
       <c r="L9">
-        <v>0.4826013975358696</v>
+        <v>0.4605939837137338</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1405,28 +1405,28 @@
         <v>73</v>
       </c>
       <c r="F10">
-        <v>0.1340973333216859</v>
+        <v>-0.05900759988455549</v>
       </c>
       <c r="G10">
-        <v>0.3197519244333061</v>
+        <v>0.2932581451653327</v>
       </c>
       <c r="H10">
-        <v>0.4193792846105479</v>
+        <v>-0.201213848131271</v>
       </c>
       <c r="I10">
-        <v>0.6749389611037842</v>
+        <v>0.8405313636934921</v>
       </c>
       <c r="J10">
-        <v>-0.4779909981932147</v>
+        <v>-0.591149348878952</v>
       </c>
       <c r="K10">
-        <v>0.7842118754494954</v>
+        <v>0.6079454440026177</v>
       </c>
       <c r="L10">
-        <v>0.1340973322289021</v>
+        <v>-0.05900760005184692</v>
       </c>
       <c r="M10">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1443,28 +1443,28 @@
         <v>62</v>
       </c>
       <c r="F11">
-        <v>-0.248328147438111</v>
+        <v>-0.236731263043929</v>
       </c>
       <c r="G11">
-        <v>0.2098046458460861</v>
+        <v>0.1591794233025839</v>
       </c>
       <c r="H11">
-        <v>-1.183616055958484</v>
+        <v>-1.487197642335511</v>
       </c>
       <c r="I11">
-        <v>0.2365650817011808</v>
+        <v>0.1369626185825394</v>
       </c>
       <c r="J11">
-        <v>-0.6689427061096573</v>
+        <v>-0.5561971589264326</v>
       </c>
       <c r="K11">
-        <v>0.1599606373303642</v>
+        <v>0.07571901833144189</v>
       </c>
       <c r="L11">
-        <v>-0.2647263262425801</v>
+        <v>-0.2741822366148256</v>
       </c>
       <c r="M11">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1481,28 +1481,28 @@
         <v>64</v>
       </c>
       <c r="F12">
-        <v>-0.3881960980567967</v>
+        <v>-0.2118437185458557</v>
       </c>
       <c r="G12">
-        <v>0.2170098703321209</v>
+        <v>0.2078481145773414</v>
       </c>
       <c r="H12">
-        <v>-1.788840744721359</v>
+        <v>-1.01922367194256</v>
       </c>
       <c r="I12">
-        <v>0.07364046697785054</v>
+        <v>0.3080967908965351</v>
       </c>
       <c r="J12">
-        <v>-0.7418810217495119</v>
+        <v>-0.616104636287977</v>
       </c>
       <c r="K12">
-        <v>0.09968245146019813</v>
+        <v>0.1924790931379436</v>
       </c>
       <c r="L12">
-        <v>-0.4155736263304021</v>
+        <v>-0.2430565166523081</v>
       </c>
       <c r="M12">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1519,28 +1519,28 @@
         <v>66</v>
       </c>
       <c r="F13">
-        <v>0.2863211021265075</v>
+        <v>0.3584423697409252</v>
       </c>
       <c r="G13">
-        <v>0.1952831887429846</v>
+        <v>0.1820970846021392</v>
       </c>
       <c r="H13">
-        <v>1.466184078463299</v>
+        <v>1.968413555461801</v>
       </c>
       <c r="I13">
-        <v>0.1425981449174742</v>
+        <v>0.04902047346450766</v>
       </c>
       <c r="J13">
-        <v>-0.1187623037795397</v>
+        <v>-0.03621295245964663</v>
       </c>
       <c r="K13">
-        <v>0.6376082759570304</v>
+        <v>0.6735765551479445</v>
       </c>
       <c r="L13">
-        <v>0.3059581319498312</v>
+        <v>0.4086944881647628</v>
       </c>
       <c r="M13">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1557,28 +1557,28 @@
         <v>64</v>
       </c>
       <c r="F14">
-        <v>-0.1369189125330285</v>
+        <v>-0.1689091322025419</v>
       </c>
       <c r="G14">
-        <v>0.2226580566746807</v>
+        <v>0.1985880162307288</v>
       </c>
       <c r="H14">
-        <v>-0.6149290736560985</v>
+        <v>-0.8505504783646933</v>
       </c>
       <c r="I14">
-        <v>0.5386015614724269</v>
+        <v>0.3950191085198687</v>
       </c>
       <c r="J14">
-        <v>-0.5747604008325157</v>
+        <v>-0.5573146541550374</v>
       </c>
       <c r="K14">
-        <v>0.2926371598310396</v>
+        <v>0.2034325060354614</v>
       </c>
       <c r="L14">
-        <v>-0.1455943439567093</v>
+        <v>-0.180720295416524</v>
       </c>
       <c r="M14">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1595,28 +1595,28 @@
         <v>66</v>
       </c>
       <c r="F15">
-        <v>-0.4094987878636694</v>
+        <v>-0.3848150919051239</v>
       </c>
       <c r="G15">
-        <v>0.1464749869224694</v>
+        <v>0.1391085957698361</v>
       </c>
       <c r="H15">
-        <v>-2.795690898954788</v>
+        <v>-2.766292692234668</v>
       </c>
       <c r="I15">
-        <v>0.005178890604623065</v>
+        <v>0.005669762107538778</v>
       </c>
       <c r="J15">
-        <v>-0.6605975073365692</v>
+        <v>-0.6331488375144596</v>
       </c>
       <c r="K15">
-        <v>-0.08800700379846689</v>
+        <v>-0.09803492012155185</v>
       </c>
       <c r="L15">
-        <v>-0.4346558354460115</v>
+        <v>-0.409160457578904</v>
       </c>
       <c r="M15">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1633,28 +1633,28 @@
         <v>66</v>
       </c>
       <c r="F16">
-        <v>0.2933972252029525</v>
+        <v>0.340692764034311</v>
       </c>
       <c r="G16">
-        <v>0.1763663679484545</v>
+        <v>0.1707713017577692</v>
       </c>
       <c r="H16">
-        <v>1.663566748104161</v>
+        <v>1.995023522849098</v>
       </c>
       <c r="I16">
-        <v>0.09619904156800585</v>
+        <v>0.04604031438599376</v>
       </c>
       <c r="J16">
-        <v>-0.0689387511294849</v>
+        <v>-0.01306069681412388</v>
       </c>
       <c r="K16">
-        <v>0.6212956871596268</v>
+        <v>0.6604237264780218</v>
       </c>
       <c r="L16">
-        <v>0.3127335857087495</v>
+        <v>0.3588495847739033</v>
       </c>
       <c r="M16">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1674,28 +1674,28 @@
         <v>78</v>
       </c>
       <c r="F17">
-        <v>-0.01379512085308073</v>
+        <v>-0.08966941234656185</v>
       </c>
       <c r="G17">
-        <v>0.09706123988341031</v>
+        <v>0.1644596375445589</v>
       </c>
       <c r="H17">
-        <v>-0.142128009797231</v>
+        <v>-0.5452365923053109</v>
       </c>
       <c r="I17">
-        <v>0.8869788941369345</v>
+        <v>0.5855908075105269</v>
       </c>
       <c r="J17">
-        <v>-0.2827289224971024</v>
+        <v>-0.5411689399528838</v>
       </c>
       <c r="K17">
-        <v>0.123308326752328</v>
+        <v>0.1119226776907945</v>
       </c>
       <c r="L17">
-        <v>-0.01379512079794074</v>
+        <v>-0.08966941237589242</v>
       </c>
       <c r="M17">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1715,28 +1715,28 @@
         <v>81</v>
       </c>
       <c r="F18">
-        <v>-0.0006501812653554213</v>
+        <v>0.02173678709059068</v>
       </c>
       <c r="G18">
-        <v>0.07851450477465306</v>
+        <v>0.08880989547307132</v>
       </c>
       <c r="H18">
-        <v>-0.008281033768493184</v>
+        <v>0.2447563638579177</v>
       </c>
       <c r="I18">
-        <v>0.993392766524464</v>
+        <v>0.8066450829488945</v>
       </c>
       <c r="J18">
-        <v>-0.162549770670685</v>
+        <v>-0.07847473031028127</v>
       </c>
       <c r="K18">
-        <v>0.1684305434778464</v>
+        <v>0.260876952877951</v>
       </c>
       <c r="L18">
-        <v>-0.0006501812627566046</v>
+        <v>0.02173678709770072</v>
       </c>
       <c r="M18">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1756,28 +1756,28 @@
         <v>84</v>
       </c>
       <c r="F19">
-        <v>0.05176491103594025</v>
+        <v>0.05375743683002785</v>
       </c>
       <c r="G19">
-        <v>0.1877456151309055</v>
+        <v>0.1299695983096516</v>
       </c>
       <c r="H19">
-        <v>0.2757183490003066</v>
+        <v>0.4136154726119193</v>
       </c>
       <c r="I19">
-        <v>0.7827644012514849</v>
+        <v>0.6791557399549943</v>
       </c>
       <c r="J19">
-        <v>-0.3975469004468558</v>
+        <v>-0.1893481627692</v>
       </c>
       <c r="K19">
-        <v>0.384123698038462</v>
+        <v>0.3385900792271178</v>
       </c>
       <c r="L19">
-        <v>0.05176491082903253</v>
+        <v>0.05375743684761174</v>
       </c>
       <c r="M19">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1797,28 +1797,28 @@
         <v>87</v>
       </c>
       <c r="F20">
-        <v>-0.01192693441499119</v>
+        <v>0.002064899202602467</v>
       </c>
       <c r="G20">
-        <v>0.06816411204130765</v>
+        <v>0.06504702767566659</v>
       </c>
       <c r="H20">
-        <v>-0.1749738103793303</v>
+        <v>0.03174471265464025</v>
       </c>
       <c r="I20">
-        <v>0.8611002123886407</v>
+        <v>0.9746756372969105</v>
       </c>
       <c r="J20">
-        <v>-0.1936142801163783</v>
+        <v>-0.1483840499824843</v>
       </c>
       <c r="K20">
-        <v>0.08735538863259122</v>
+        <v>0.1353272578484186</v>
       </c>
       <c r="L20">
-        <v>-0.01192693436731845</v>
+        <v>0.00206489920327789</v>
       </c>
       <c r="M20">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1838,28 +1838,28 @@
         <v>88</v>
       </c>
       <c r="F21">
-        <v>0.0253926745025129</v>
+        <v>-0.01211028922334085</v>
       </c>
       <c r="G21">
-        <v>0.2474037228179007</v>
+        <v>0.2050155203246768</v>
       </c>
       <c r="H21">
-        <v>0.1026365901583581</v>
+        <v>-0.05907010944421259</v>
       </c>
       <c r="I21">
-        <v>0.9182514014322076</v>
+        <v>0.9528962662634057</v>
       </c>
       <c r="J21">
-        <v>-0.5843026102505494</v>
+        <v>-0.4276890583758312</v>
       </c>
       <c r="K21">
-        <v>0.4150129950884399</v>
+        <v>0.3945098423560491</v>
       </c>
       <c r="L21">
-        <v>0.02539267440101674</v>
+        <v>-0.01211028922730207</v>
       </c>
       <c r="M21">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1879,28 +1879,28 @@
         <v>90</v>
       </c>
       <c r="F22">
-        <v>0.4692488926256184</v>
+        <v>0.162163592138079</v>
       </c>
       <c r="G22">
-        <v>0.2351990864484656</v>
+        <v>0.2605522124944769</v>
       </c>
       <c r="H22">
-        <v>1.99511358530908</v>
+        <v>0.6223842453132746</v>
       </c>
       <c r="I22">
-        <v>0.04603049299452211</v>
+        <v>0.5336892374190216</v>
       </c>
       <c r="J22">
-        <v>-0.009420621797506447</v>
+        <v>-0.2245066739369579</v>
       </c>
       <c r="K22">
-        <v>0.9064294185865254</v>
+        <v>0.7869045106666488</v>
       </c>
       <c r="L22">
-        <v>0.46924889075</v>
+        <v>0.1621635921911222</v>
       </c>
       <c r="M22">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1920,28 +1920,28 @@
         <v>94</v>
       </c>
       <c r="F23">
-        <v>-0.01314493958772531</v>
+        <v>-0.1114061994371525</v>
       </c>
       <c r="G23">
-        <v>0.1233483180399397</v>
+        <v>0.2047064069134752</v>
       </c>
       <c r="H23">
-        <v>-0.1065676435366474</v>
+        <v>-0.5442242923263336</v>
       </c>
       <c r="I23">
-        <v>0.9151319890836882</v>
+        <v>0.5862871371845571</v>
       </c>
       <c r="J23">
-        <v>-0.3160759881729552</v>
+        <v>-0.706300316364833</v>
       </c>
       <c r="K23">
-        <v>0.1737600537256887</v>
+        <v>0.1222560441969727</v>
       </c>
       <c r="L23">
-        <v>-0.01314493953518413</v>
+        <v>-0.1114061994735931</v>
       </c>
       <c r="M23">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1961,28 +1961,28 @@
         <v>97</v>
       </c>
       <c r="F24">
-        <v>-0.06556003188902099</v>
+        <v>-0.1434268491765897</v>
       </c>
       <c r="G24">
-        <v>0.2037736011026745</v>
+        <v>0.2155244504041514</v>
       </c>
       <c r="H24">
-        <v>-0.3217297605492457</v>
+        <v>-0.6654783200125819</v>
       </c>
       <c r="I24">
-        <v>0.7476574299455061</v>
+        <v>0.5057446056742996</v>
       </c>
       <c r="J24">
-        <v>-0.4258980642091154</v>
+        <v>-0.6555172953164511</v>
       </c>
       <c r="K24">
-        <v>0.4097582320284656</v>
+        <v>0.2497202110673001</v>
       </c>
       <c r="L24">
-        <v>-0.06556003162697327</v>
+        <v>-0.1434268492235042</v>
       </c>
       <c r="M24">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2002,28 +2002,28 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>-0.001868186438089543</v>
+        <v>-0.09173431154916432</v>
       </c>
       <c r="G25">
-        <v>0.1217971993130217</v>
+        <v>0.1890850423705143</v>
       </c>
       <c r="H25">
-        <v>-0.01533850079169932</v>
+        <v>-0.4851484305639042</v>
       </c>
       <c r="I25">
-        <v>0.9877621269009202</v>
+        <v>0.6275710598340589</v>
       </c>
       <c r="J25">
-        <v>-0.293395653822604</v>
+        <v>-0.5892180253508644</v>
       </c>
       <c r="K25">
-        <v>0.2334253384104693</v>
+        <v>0.1550550752557589</v>
       </c>
       <c r="L25">
-        <v>-0.001868186430622282</v>
+        <v>-0.09173431157917031</v>
       </c>
       <c r="M25">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2043,28 +2043,28 @@
         <v>103</v>
       </c>
       <c r="F26">
-        <v>-0.05241509230129567</v>
+        <v>-0.03202064973943716</v>
       </c>
       <c r="G26">
-        <v>0.2000648953959787</v>
+        <v>0.1553428627271248</v>
       </c>
       <c r="H26">
-        <v>-0.2619904516359706</v>
+        <v>-0.2061288763274861</v>
       </c>
       <c r="I26">
-        <v>0.793328803644934</v>
+        <v>0.8366902430394954</v>
       </c>
       <c r="J26">
-        <v>-0.3959486540344582</v>
+        <v>-0.3440177362752985</v>
       </c>
       <c r="K26">
-        <v>0.4347772473983176</v>
+        <v>0.2786650830156297</v>
       </c>
       <c r="L26">
-        <v>-0.05241509209178914</v>
+        <v>-0.03202064974991102</v>
       </c>
       <c r="M26">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -2084,28 +2084,28 @@
         <v>106</v>
       </c>
       <c r="F27">
-        <v>0.01127675314963577</v>
+        <v>0.01967188788798822</v>
       </c>
       <c r="G27">
-        <v>0.1024077728907155</v>
+        <v>0.1106778133825401</v>
       </c>
       <c r="H27">
-        <v>0.1101161838727785</v>
+        <v>0.1777401205063159</v>
       </c>
       <c r="I27">
-        <v>0.9123172333359078</v>
+        <v>0.8589270752776186</v>
       </c>
       <c r="J27">
-        <v>-0.1747407030268678</v>
+        <v>-0.1401048143832075</v>
       </c>
       <c r="K27">
-        <v>0.2387831720577824</v>
+        <v>0.2913274068561475</v>
       </c>
       <c r="L27">
-        <v>0.01127675310456185</v>
+        <v>0.01967188789442283</v>
       </c>
       <c r="M27">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -2125,28 +2125,28 @@
         <v>109</v>
       </c>
       <c r="F28">
-        <v>0.06369184545093144</v>
+        <v>0.05169253762742539</v>
       </c>
       <c r="G28">
-        <v>0.196534306072444</v>
+        <v>0.1473381379231265</v>
       </c>
       <c r="H28">
-        <v>0.3240749501893789</v>
+        <v>0.3508428866828486</v>
       </c>
       <c r="I28">
-        <v>0.7458812912334489</v>
+        <v>0.7257062208392773</v>
       </c>
       <c r="J28">
-        <v>-0.3901180448184062</v>
+        <v>-0.2253022944731676</v>
       </c>
       <c r="K28">
-        <v>0.4112308530897452</v>
+        <v>0.3791886104549344</v>
       </c>
       <c r="L28">
-        <v>0.06369184519635099</v>
+        <v>0.05169253764433385</v>
       </c>
       <c r="M28">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2166,28 +2166,28 @@
         <v>61</v>
       </c>
       <c r="F29">
-        <v>0.3522932556069948</v>
+        <v>0.3270279759063124</v>
       </c>
       <c r="G29">
-        <v>0.237004994854157</v>
+        <v>0.1917914203484117</v>
       </c>
       <c r="H29">
-        <v>1.486438105761363</v>
+        <v>1.705123072305464</v>
       </c>
       <c r="I29">
-        <v>0.1371632768817723</v>
+        <v>0.08817147338166831</v>
       </c>
       <c r="J29">
-        <v>-0.3216551933291154</v>
+        <v>0.01304434089286211</v>
       </c>
       <c r="K29">
-        <v>0.6748301390466247</v>
+        <v>0.6694365371529677</v>
       </c>
       <c r="L29">
-        <v>0.3522932630524714</v>
+        <v>0.3270279747320885</v>
       </c>
       <c r="M29">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2207,28 +2207,28 @@
         <v>63</v>
       </c>
       <c r="F30">
-        <v>-0.01697030278621311</v>
+        <v>-0.2645061627634546</v>
       </c>
       <c r="G30">
-        <v>0.2702982163522204</v>
+        <v>0.252268723788479</v>
       </c>
       <c r="H30">
-        <v>-0.06278362845021306</v>
+        <v>-1.048509536938223</v>
       </c>
       <c r="I30">
-        <v>0.9499388027512117</v>
+        <v>0.2944039106686536</v>
       </c>
       <c r="J30">
-        <v>-0.5022166743200334</v>
+        <v>-0.667925128378156</v>
       </c>
       <c r="K30">
-        <v>0.6039755745271218</v>
+        <v>0.2993695682981449</v>
       </c>
       <c r="L30">
-        <v>-0.01697030263815531</v>
+        <v>-0.2645061619305895</v>
       </c>
       <c r="M30">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2248,28 +2248,28 @@
         <v>65</v>
       </c>
       <c r="F31">
-        <v>0.1318121803859448</v>
+        <v>0.186143151641138</v>
       </c>
       <c r="G31">
-        <v>0.2251893656689332</v>
+        <v>0.1978061308776113</v>
       </c>
       <c r="H31">
-        <v>0.5853392765435076</v>
+        <v>0.9410383329135055</v>
       </c>
       <c r="I31">
-        <v>0.5583196103087542</v>
+        <v>0.3466852154356925</v>
       </c>
       <c r="J31">
-        <v>-0.4233089496093723</v>
+        <v>-0.1902253490290741</v>
       </c>
       <c r="K31">
-        <v>0.530359733987785</v>
+        <v>0.5609844661336318</v>
       </c>
       <c r="L31">
-        <v>0.131812178961201</v>
+        <v>0.1861431518345786</v>
       </c>
       <c r="M31">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -2289,28 +2289,28 @@
         <v>67</v>
       </c>
       <c r="F32">
-        <v>0.2212517115230526</v>
+        <v>0.1710408821198427</v>
       </c>
       <c r="G32">
-        <v>0.2850267465438066</v>
+        <v>0.2954115446352411</v>
       </c>
       <c r="H32">
-        <v>0.7762489457776124</v>
+        <v>0.578991868212311</v>
       </c>
       <c r="I32">
-        <v>0.4376020113577261</v>
+        <v>0.5625946601176175</v>
       </c>
       <c r="J32">
-        <v>-0.3556374099766806</v>
+        <v>-0.3409094466604561</v>
       </c>
       <c r="K32">
-        <v>0.7511021098768424</v>
+        <v>0.8182501529621226</v>
       </c>
       <c r="L32">
-        <v>0.2212517145610836</v>
+        <v>0.1710408822905684</v>
       </c>
       <c r="M32">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -2330,28 +2330,28 @@
         <v>69</v>
       </c>
       <c r="F33">
-        <v>-0.5278428931269867</v>
+        <v>0.2063807989375194</v>
       </c>
       <c r="G33">
-        <v>0.2237331348052193</v>
+        <v>0.3397561298391212</v>
       </c>
       <c r="H33">
-        <v>-2.359252211732175</v>
+        <v>0.6074380439736091</v>
       </c>
       <c r="I33">
-        <v>0.01831180553069855</v>
+        <v>0.5435602474100627</v>
       </c>
       <c r="J33">
-        <v>-0.9855103924032889</v>
+        <v>-0.6081852582140502</v>
       </c>
       <c r="K33">
-        <v>-0.09905814833093818</v>
+        <v>0.6124184313495469</v>
       </c>
       <c r="L33">
-        <v>-0.5278428953186268</v>
+        <v>0.2063807989149683</v>
       </c>
       <c r="M33">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2371,28 +2371,28 @@
         <v>70</v>
       </c>
       <c r="F34">
-        <v>-0.2143437882396327</v>
+        <v>-0.2618844256276633</v>
       </c>
       <c r="G34">
-        <v>0.2500675278870445</v>
+        <v>0.2722482921162938</v>
       </c>
       <c r="H34">
-        <v>-0.8571436285660077</v>
+        <v>-0.9619322993431177</v>
       </c>
       <c r="I34">
-        <v>0.3913655120266879</v>
+        <v>0.336083612591938</v>
       </c>
       <c r="J34">
-        <v>-0.7141110011853673</v>
+        <v>-0.8258164861332248</v>
       </c>
       <c r="K34">
-        <v>0.2086185139427386</v>
+        <v>0.2231103881457986</v>
       </c>
       <c r="L34">
-        <v>-0.2143437845995938</v>
+        <v>-0.2618844265393674</v>
       </c>
       <c r="M34">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2412,28 +2412,28 @@
         <v>71</v>
       </c>
       <c r="F35">
-        <v>0.06253675557628689</v>
+        <v>0.07442281339650943</v>
       </c>
       <c r="G35">
-        <v>0.2606557316839331</v>
+        <v>0.2544290205973972</v>
       </c>
       <c r="H35">
-        <v>0.2399208917151991</v>
+        <v>0.2925091376045282</v>
       </c>
       <c r="I35">
-        <v>0.8103915845576941</v>
+        <v>0.7698973744439686</v>
       </c>
       <c r="J35">
-        <v>-0.3938835677964082</v>
+        <v>-0.4385412331816506</v>
       </c>
       <c r="K35">
-        <v>0.5127140774435611</v>
+        <v>0.5456448756560983</v>
       </c>
       <c r="L35">
-        <v>0.0625367563815472</v>
+        <v>0.07442281362271654</v>
       </c>
       <c r="M35">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2453,28 +2453,28 @@
         <v>72</v>
       </c>
       <c r="F36">
-        <v>-0.1401445803354107</v>
+        <v>-0.1566711941004187</v>
       </c>
       <c r="G36">
-        <v>0.2905275694965176</v>
+        <v>0.3021148105354888</v>
       </c>
       <c r="H36">
-        <v>-0.482379626065369</v>
+        <v>-0.518581640611144</v>
       </c>
       <c r="I36">
-        <v>0.6295362916742624</v>
+        <v>0.6040525146670663</v>
       </c>
       <c r="J36">
-        <v>-0.754259973973866</v>
+        <v>-0.767256804204002</v>
       </c>
       <c r="K36">
-        <v>0.3604555943992547</v>
+        <v>0.4435478028811393</v>
       </c>
       <c r="L36">
-        <v>-0.1401445824321084</v>
+        <v>-0.1566711939204862</v>
       </c>
       <c r="M36">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2494,28 +2494,28 @@
         <v>73</v>
       </c>
       <c r="F37">
-        <v>0.7389599649246605</v>
+        <v>0.5832880460930159</v>
       </c>
       <c r="G37">
-        <v>0.3258511064033368</v>
+        <v>0.2990196220759521</v>
       </c>
       <c r="H37">
-        <v>2.267784121039564</v>
+        <v>1.950668126872485</v>
       </c>
       <c r="I37">
-        <v>0.02334236769527065</v>
+        <v>0.05109653725275654</v>
       </c>
       <c r="J37">
-        <v>0.06378064641426165</v>
+        <v>0.1316922702887037</v>
       </c>
       <c r="K37">
-        <v>1.299394564636793</v>
+        <v>1.281942519408654</v>
       </c>
       <c r="L37">
-        <v>0.738959957846135</v>
+        <v>0.5832880454470675</v>
       </c>
       <c r="M37">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2532,28 +2532,28 @@
         <v>62</v>
       </c>
       <c r="F38">
-        <v>-0.1275458562376721</v>
+        <v>-0.09109817712014077</v>
       </c>
       <c r="G38">
-        <v>0.184809991799524</v>
+        <v>0.149802458330874</v>
       </c>
       <c r="H38">
-        <v>-0.6901458898176341</v>
+        <v>-0.6081220437579801</v>
       </c>
       <c r="I38">
-        <v>0.4901024472122808</v>
+        <v>0.5431065330003642</v>
       </c>
       <c r="J38">
-        <v>-0.4821684522535891</v>
+        <v>-0.3927131438927841</v>
       </c>
       <c r="K38">
-        <v>0.2463107934618337</v>
+        <v>0.206607452425901</v>
       </c>
       <c r="L38">
-        <v>-0.1448215508461737</v>
+        <v>-0.1049567668149467</v>
       </c>
       <c r="M38">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2570,28 +2570,28 @@
         <v>64</v>
       </c>
       <c r="F39">
-        <v>0.2295768243703263</v>
+        <v>0.2042631818696823</v>
       </c>
       <c r="G39">
-        <v>0.2099877559284339</v>
+        <v>0.1969019330861654</v>
       </c>
       <c r="H39">
-        <v>1.093286717386363</v>
+        <v>1.037385355583561</v>
       </c>
       <c r="I39">
-        <v>0.2742679329159916</v>
+        <v>0.2995563004958126</v>
       </c>
       <c r="J39">
-        <v>-0.2492033617376874</v>
+        <v>-0.2201856814334468</v>
       </c>
       <c r="K39">
-        <v>0.5795634434496958</v>
+        <v>0.5525074566767896</v>
       </c>
       <c r="L39">
-        <v>0.2629288924241074</v>
+        <v>0.2309927141925711</v>
       </c>
       <c r="M39">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2608,28 +2608,28 @@
         <v>66</v>
       </c>
       <c r="F40">
-        <v>0.2499710974291127</v>
+        <v>0.2103519386749301</v>
       </c>
       <c r="G40">
-        <v>0.1737584290367588</v>
+        <v>0.1444530911210437</v>
       </c>
       <c r="H40">
-        <v>1.438612784512635</v>
+        <v>1.456195482162904</v>
       </c>
       <c r="I40">
-        <v>0.1502602621109816</v>
+        <v>0.1453385880959472</v>
       </c>
       <c r="J40">
-        <v>-0.1177556811447976</v>
+        <v>-0.07668964100950908</v>
       </c>
       <c r="K40">
-        <v>0.5650955420573789</v>
+        <v>0.4841266101574303</v>
       </c>
       <c r="L40">
-        <v>0.2909999781650473</v>
+        <v>0.237216387148276</v>
       </c>
       <c r="M40">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2646,28 +2646,28 @@
         <v>64</v>
       </c>
       <c r="F41">
-        <v>0.06112403328104325</v>
+        <v>0.06586835976784823</v>
       </c>
       <c r="G41">
-        <v>0.1798407213499092</v>
+        <v>0.1525709859222421</v>
       </c>
       <c r="H41">
-        <v>0.3398787150220364</v>
+        <v>0.431722711691842</v>
       </c>
       <c r="I41">
-        <v>0.7339478664137156</v>
+        <v>0.6659429584966179</v>
       </c>
       <c r="J41">
-        <v>-0.2837267708250059</v>
+        <v>-0.2285889617370188</v>
       </c>
       <c r="K41">
-        <v>0.4146338579015895</v>
+        <v>0.3687474215804115</v>
       </c>
       <c r="L41">
-        <v>0.06552536566082118</v>
+        <v>0.07299171851431155</v>
       </c>
       <c r="M41">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2684,28 +2684,28 @@
         <v>66</v>
       </c>
       <c r="F42">
-        <v>0.0845089267668737</v>
+        <v>0.04487417729071017</v>
       </c>
       <c r="G42">
-        <v>0.1839343720089363</v>
+        <v>0.1543532304340585</v>
       </c>
       <c r="H42">
-        <v>0.4594515198212539</v>
+        <v>0.2907239269597338</v>
       </c>
       <c r="I42">
-        <v>0.6459099585710506</v>
+        <v>0.7712624705608619</v>
       </c>
       <c r="J42">
-        <v>-0.2691170161451841</v>
+        <v>-0.2717492330842776</v>
       </c>
       <c r="K42">
-        <v>0.4574489479414391</v>
+        <v>0.3436392738827322</v>
       </c>
       <c r="L42">
-        <v>0.09208585563214439</v>
+        <v>0.04958875655339038</v>
       </c>
       <c r="M42">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2722,28 +2722,28 @@
         <v>66</v>
       </c>
       <c r="F43">
-        <v>0.3896024354013992</v>
+        <v>0.47482621577533</v>
       </c>
       <c r="G43">
-        <v>0.1621963389552965</v>
+        <v>0.1576620663539997</v>
       </c>
       <c r="H43">
-        <v>2.402042104715933</v>
+        <v>3.011670636798578</v>
       </c>
       <c r="I43">
-        <v>0.01630383172972083</v>
+        <v>0.002598143316950186</v>
       </c>
       <c r="J43">
-        <v>0.008720200102017926</v>
+        <v>0.1093042277056609</v>
       </c>
       <c r="K43">
-        <v>0.638051038517172</v>
+        <v>0.7177002538747269</v>
       </c>
       <c r="L43">
-        <v>0.428208646013166</v>
+        <v>0.5150256275917524</v>
       </c>
       <c r="M43">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2763,28 +2763,28 @@
         <v>78</v>
       </c>
       <c r="F44">
-        <v>-0.07551187097807646</v>
+        <v>-0.08564353363440193</v>
       </c>
       <c r="G44">
-        <v>0.1211085492931236</v>
+        <v>0.1231753885845921</v>
       </c>
       <c r="H44">
-        <v>-0.6235057014456695</v>
+        <v>-0.6952974503959877</v>
       </c>
       <c r="I44">
-        <v>0.5329522567714688</v>
+        <v>0.4868689117474621</v>
       </c>
       <c r="J44">
-        <v>-0.314547219644992</v>
+        <v>-0.3885211891534668</v>
       </c>
       <c r="K44">
-        <v>0.125316180866851</v>
+        <v>0.05422294683398064</v>
       </c>
       <c r="L44">
-        <v>-0.07551187129160697</v>
+        <v>-0.08564353362504375</v>
       </c>
       <c r="M44">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2804,28 +2804,28 @@
         <v>81</v>
       </c>
       <c r="F45">
-        <v>-0.001061267677396989</v>
+        <v>-0.01968529279357133</v>
       </c>
       <c r="G45">
-        <v>0.07152871240250074</v>
+        <v>0.1013759060035073</v>
       </c>
       <c r="H45">
-        <v>-0.01483694647577476</v>
+        <v>-0.1941811774573959</v>
       </c>
       <c r="I45">
-        <v>0.9881622637957528</v>
+        <v>0.8460340205710193</v>
       </c>
       <c r="J45">
-        <v>-0.1421081681523532</v>
+        <v>-0.2104817106114766</v>
       </c>
       <c r="K45">
-        <v>0.09549358632725466</v>
+        <v>0.2088106624030726</v>
       </c>
       <c r="L45">
-        <v>-0.001061267681803446</v>
+        <v>-0.01968529279142034</v>
       </c>
       <c r="M45">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2845,28 +2845,28 @@
         <v>84</v>
       </c>
       <c r="F46">
-        <v>-0.01847276270328368</v>
+        <v>-0.02916326984123241</v>
       </c>
       <c r="G46">
-        <v>0.07628457088996213</v>
+        <v>0.08627307773519942</v>
       </c>
       <c r="H46">
-        <v>-0.242155949594709</v>
+        <v>-0.3380344205494108</v>
       </c>
       <c r="I46">
-        <v>0.8086593264606803</v>
+        <v>0.7353372491156702</v>
       </c>
       <c r="J46">
-        <v>-0.2088823030289577</v>
+        <v>-0.2385999940261567</v>
       </c>
       <c r="K46">
-        <v>0.07836168568735258</v>
+        <v>0.1075636825620861</v>
       </c>
       <c r="L46">
-        <v>-0.01847276277998387</v>
+        <v>-0.02916326983804577</v>
       </c>
       <c r="M46">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2886,28 +2886,28 @@
         <v>87</v>
       </c>
       <c r="F47">
-        <v>0.1634961569865961</v>
+        <v>0.09976610193370891</v>
       </c>
       <c r="G47">
-        <v>0.2322581215606281</v>
+        <v>0.234080452387484</v>
       </c>
       <c r="H47">
-        <v>0.7039416141317472</v>
+        <v>0.4262043281109247</v>
       </c>
       <c r="I47">
-        <v>0.4814691345472721</v>
+        <v>0.6699589639854922</v>
       </c>
       <c r="J47">
-        <v>-0.2315461823200897</v>
+        <v>-0.2580126552397989</v>
       </c>
       <c r="K47">
-        <v>0.6613977789990788</v>
+        <v>0.7191682083783921</v>
       </c>
       <c r="L47">
-        <v>0.1634961576654434</v>
+        <v>0.09976610192280755</v>
       </c>
       <c r="M47">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2927,28 +2927,28 @@
         <v>88</v>
       </c>
       <c r="F48">
-        <v>0.06845025562783894</v>
+        <v>-0.03472599433549675</v>
       </c>
       <c r="G48">
-        <v>0.2291866613168793</v>
+        <v>0.252655467404076</v>
       </c>
       <c r="H48">
-        <v>0.29866596613665</v>
+        <v>-0.1374440644102861</v>
       </c>
       <c r="I48">
-        <v>0.7651949274897687</v>
+        <v>0.8906798031518055</v>
       </c>
       <c r="J48">
-        <v>-0.3463067618842783</v>
+        <v>-0.4800063582472885</v>
       </c>
       <c r="K48">
-        <v>0.5126256694814622</v>
+        <v>0.547536180335071</v>
       </c>
       <c r="L48">
-        <v>0.06845025591204912</v>
+        <v>-0.03472599433170231</v>
       </c>
       <c r="M48">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2968,28 +2968,28 @@
         <v>90</v>
       </c>
       <c r="F49">
-        <v>-0.4593926374991478</v>
+        <v>0.1716548046020226</v>
       </c>
       <c r="G49">
-        <v>0.2511851609401504</v>
+        <v>0.2732474535014829</v>
       </c>
       <c r="H49">
-        <v>-1.828900384798634</v>
+        <v>0.6282027605468282</v>
       </c>
       <c r="I49">
-        <v>0.06741453259358909</v>
+        <v>0.5298711221318164</v>
       </c>
       <c r="J49">
-        <v>-0.9415964524615551</v>
+        <v>-0.3480595377567794</v>
       </c>
       <c r="K49">
-        <v>-0.005657997153639442</v>
+        <v>0.48698397185857</v>
       </c>
       <c r="L49">
-        <v>-0.4593926394065777</v>
+        <v>0.171654804583266</v>
       </c>
       <c r="M49">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -3009,28 +3009,28 @@
         <v>94</v>
       </c>
       <c r="F50">
-        <v>-0.07445060330067947</v>
+        <v>-0.0659582408408306</v>
       </c>
       <c r="G50">
-        <v>0.1400952945299878</v>
+        <v>0.16468415690999</v>
       </c>
       <c r="H50">
-        <v>-0.5314282935087665</v>
+        <v>-0.4005135774953801</v>
       </c>
       <c r="I50">
-        <v>0.5951220193407818</v>
+        <v>0.6887782851350015</v>
       </c>
       <c r="J50">
-        <v>-0.3344940547802284</v>
+        <v>-0.4703892443648931</v>
       </c>
       <c r="K50">
-        <v>0.2012415650051572</v>
+        <v>0.1709016518071516</v>
       </c>
       <c r="L50">
-        <v>-0.07445060360980352</v>
+        <v>-0.06595824083362341</v>
       </c>
       <c r="M50">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -3050,28 +3050,28 @@
         <v>97</v>
       </c>
       <c r="F51">
-        <v>-0.05703910827479278</v>
+        <v>-0.05648026379316952</v>
       </c>
       <c r="G51">
-        <v>0.1432485558089512</v>
+        <v>0.149635742334569</v>
       </c>
       <c r="H51">
-        <v>-0.3981827806408403</v>
+        <v>-0.3774516897633046</v>
       </c>
       <c r="I51">
-        <v>0.6904954578702571</v>
+        <v>0.7058379597465201</v>
       </c>
       <c r="J51">
-        <v>-0.3286069831118746</v>
+        <v>-0.4086795542680349</v>
       </c>
       <c r="K51">
-        <v>0.207143680061023</v>
+        <v>0.1842377562072706</v>
       </c>
       <c r="L51">
-        <v>-0.0570391085116231</v>
+        <v>-0.05648026378699798</v>
       </c>
       <c r="M51">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -3091,28 +3091,28 @@
         <v>100</v>
       </c>
       <c r="F52">
-        <v>-0.2390080279646725</v>
+        <v>-0.1854096355681109</v>
       </c>
       <c r="G52">
-        <v>0.291618869820331</v>
+        <v>0.2750438193101768</v>
       </c>
       <c r="H52">
-        <v>-0.8195904061761418</v>
+        <v>-0.6741094420268275</v>
       </c>
       <c r="I52">
-        <v>0.4124496446456833</v>
+        <v>0.5002417370504906</v>
       </c>
       <c r="J52">
-        <v>-0.8662020200788551</v>
+        <v>-0.9027297117509715</v>
       </c>
       <c r="K52">
-        <v>0.2855535971785857</v>
+        <v>0.1938446281845205</v>
       </c>
       <c r="L52">
-        <v>-0.2390080289570504</v>
+        <v>-0.1854096355478513</v>
       </c>
       <c r="M52">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -3132,28 +3132,28 @@
         <v>103</v>
       </c>
       <c r="F53">
-        <v>0.01741149502588669</v>
+        <v>0.009477977047661075</v>
       </c>
       <c r="G53">
-        <v>0.1082961710085189</v>
+        <v>0.126768778578292</v>
       </c>
       <c r="H53">
-        <v>0.1607766448595587</v>
+        <v>0.07476586233579199</v>
       </c>
       <c r="I53">
-        <v>0.8722693206119361</v>
+        <v>0.9404010036770227</v>
       </c>
       <c r="J53">
-        <v>-0.1671329941102766</v>
+        <v>-0.2147023685369325</v>
       </c>
       <c r="K53">
-        <v>0.2292603598398735</v>
+        <v>0.2985863357940144</v>
       </c>
       <c r="L53">
-        <v>0.01741149509818042</v>
+        <v>0.009477977046625424</v>
       </c>
       <c r="M53">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -3173,28 +3173,28 @@
         <v>106</v>
       </c>
       <c r="F54">
-        <v>-0.164557424663993</v>
+        <v>-0.1194513947272803</v>
       </c>
       <c r="G54">
-        <v>0.2352034322843305</v>
+        <v>0.2611493632646583</v>
       </c>
       <c r="H54">
-        <v>-0.6996387045281908</v>
+        <v>-0.4574064176684354</v>
       </c>
       <c r="I54">
-        <v>0.4841529648399217</v>
+        <v>0.6473789523917919</v>
       </c>
       <c r="J54">
-        <v>-0.666753935843804</v>
+        <v>-0.7597605919434829</v>
       </c>
       <c r="K54">
-        <v>0.2267616702994446</v>
+        <v>0.3353433263461005</v>
       </c>
       <c r="L54">
-        <v>-0.1645574253472468</v>
+        <v>-0.1194513947142279</v>
       </c>
       <c r="M54">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -3214,28 +3214,28 @@
         <v>109</v>
       </c>
       <c r="F55">
-        <v>-0.1819689196898797</v>
+        <v>-0.1289293717749413</v>
       </c>
       <c r="G55">
-        <v>0.270967869536652</v>
+        <v>0.2783502889965796</v>
       </c>
       <c r="H55">
-        <v>-0.6715516492824106</v>
+        <v>-0.4631910828607964</v>
       </c>
       <c r="I55">
-        <v>0.5018691680603455</v>
+        <v>0.6432274073566069</v>
       </c>
       <c r="J55">
-        <v>-0.8129437837210063</v>
+        <v>-0.8469522670748649</v>
       </c>
       <c r="K55">
-        <v>0.2616109488257513</v>
+        <v>0.2856654408924872</v>
       </c>
       <c r="L55">
-        <v>-0.1819689204454273</v>
+        <v>-0.1289293717608533</v>
       </c>
       <c r="M55">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3306,28 +3306,28 @@
         <v>61</v>
       </c>
       <c r="F2">
-        <v>0.3032623719217752</v>
+        <v>0.3848394378871026</v>
       </c>
       <c r="G2">
-        <v>0.2631700359454516</v>
+        <v>0.1455181681801464</v>
       </c>
       <c r="H2">
-        <v>1.152343848083958</v>
+        <v>2.644614364652288</v>
       </c>
       <c r="I2">
-        <v>0.2491798053673879</v>
+        <v>0.008178406446420095</v>
       </c>
       <c r="J2">
-        <v>-0.1761772244726907</v>
+        <v>0.1181551750968219</v>
       </c>
       <c r="K2">
-        <v>0.8678966291675029</v>
+        <v>0.6927235768090287</v>
       </c>
       <c r="L2">
-        <v>0.3032623706348011</v>
+        <v>0.3848394369621672</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3347,28 +3347,28 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>0.1379947800360535</v>
+        <v>0.06952583097632596</v>
       </c>
       <c r="G3">
-        <v>0.2553819712867732</v>
+        <v>0.1682004562257459</v>
       </c>
       <c r="H3">
-        <v>0.5403466005871518</v>
+        <v>0.4133510249402277</v>
       </c>
       <c r="I3">
-        <v>0.588958026560046</v>
+        <v>0.679349451048346</v>
       </c>
       <c r="J3">
-        <v>-0.4087309186920889</v>
+        <v>-0.2550155012051073</v>
       </c>
       <c r="K3">
-        <v>0.6038274893621236</v>
+        <v>0.4018461044759326</v>
       </c>
       <c r="L3">
-        <v>0.1379947794504362</v>
+        <v>0.06952583080922535</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3388,28 +3388,28 @@
         <v>63</v>
       </c>
       <c r="F4">
-        <v>0.05188445384553334</v>
+        <v>-0.2137562977693241</v>
       </c>
       <c r="G4">
-        <v>0.314984127341175</v>
+        <v>0.1816315047341834</v>
       </c>
       <c r="H4">
-        <v>0.1647208520743482</v>
+        <v>-1.176867956262077</v>
       </c>
       <c r="I4">
-        <v>0.8691637035933995</v>
+        <v>0.2392482136109411</v>
       </c>
       <c r="J4">
-        <v>-0.5360119995427105</v>
+        <v>-0.5470615556366574</v>
       </c>
       <c r="K4">
-        <v>0.6850130406089554</v>
+        <v>0.1542684372106281</v>
       </c>
       <c r="L4">
-        <v>0.05188445416025984</v>
+        <v>-0.2137562982752954</v>
       </c>
       <c r="M4">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3429,28 +3429,28 @@
         <v>114</v>
       </c>
       <c r="F5">
-        <v>0.3403483007121995</v>
+        <v>0.219233441568953</v>
       </c>
       <c r="G5">
-        <v>0.2289960080092887</v>
+        <v>0.1440905856846371</v>
       </c>
       <c r="H5">
-        <v>1.486263029958121</v>
+        <v>1.521497331191205</v>
       </c>
       <c r="I5">
-        <v>0.1372095614536664</v>
+        <v>0.1281350805380661</v>
       </c>
       <c r="J5">
-        <v>-0.1090721259299342</v>
+        <v>-0.06275046398409223</v>
       </c>
       <c r="K5">
-        <v>0.796230112381024</v>
+        <v>0.499953871961209</v>
       </c>
       <c r="L5">
-        <v>0.3403483027767224</v>
+        <v>0.219233442087889</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3470,28 +3470,28 @@
         <v>65</v>
       </c>
       <c r="F6">
-        <v>0.1731056214505613</v>
+        <v>0.1487319352136641</v>
       </c>
       <c r="G6">
-        <v>0.3609806762570069</v>
+        <v>0.1679372444009367</v>
       </c>
       <c r="H6">
-        <v>0.4795426260637716</v>
+        <v>0.8856399647631378</v>
       </c>
       <c r="I6">
-        <v>0.6315526513473615</v>
+        <v>0.3758115687007828</v>
       </c>
       <c r="J6">
-        <v>-0.5056995764867448</v>
+        <v>-0.1624043179497461</v>
       </c>
       <c r="K6">
-        <v>0.8753271451132619</v>
+        <v>0.502768657976009</v>
       </c>
       <c r="L6">
-        <v>0.1731056209147398</v>
+        <v>0.1487319349996871</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3511,28 +3511,28 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>0.3241216753335413</v>
+        <v>0.2393650657925783</v>
       </c>
       <c r="G7">
-        <v>0.2729230625395496</v>
+        <v>0.1530086240955775</v>
       </c>
       <c r="H7">
-        <v>1.187593574238793</v>
+        <v>1.564389374830649</v>
       </c>
       <c r="I7">
-        <v>0.2349935706599982</v>
+        <v>0.1177261544228436</v>
       </c>
       <c r="J7">
-        <v>-0.2011965589232184</v>
+        <v>-0.04851656954677335</v>
       </c>
       <c r="K7">
-        <v>0.86902088349373</v>
+        <v>0.5473895983912153</v>
       </c>
       <c r="L7">
-        <v>0.3241216743302733</v>
+        <v>0.2393650654482097</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3552,28 +3552,28 @@
         <v>67</v>
       </c>
       <c r="F8">
-        <v>-0.001213102105891759</v>
+        <v>0.03980533706585545</v>
       </c>
       <c r="G8">
-        <v>0.2348873363670402</v>
+        <v>0.1750175655178526</v>
       </c>
       <c r="H8">
-        <v>-0.005164612637933526</v>
+        <v>0.2274362401743905</v>
       </c>
       <c r="I8">
-        <v>0.9958792536326053</v>
+        <v>0.8200845429658776</v>
       </c>
       <c r="J8">
-        <v>-0.4682025060634204</v>
+        <v>-0.2690850929925051</v>
       </c>
       <c r="K8">
-        <v>0.445362569140955</v>
+        <v>0.4236256417388162</v>
       </c>
       <c r="L8">
-        <v>-0.001213102114597608</v>
+        <v>0.03980533700591719</v>
       </c>
       <c r="M8">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3593,28 +3593,28 @@
         <v>116</v>
       </c>
       <c r="F9">
-        <v>-0.3524832028006372</v>
+        <v>-0.34774849014813</v>
       </c>
       <c r="G9">
-        <v>0.2693138759056411</v>
+        <v>0.1602303388545514</v>
       </c>
       <c r="H9">
-        <v>-1.3088193158088</v>
+        <v>-2.170303655562993</v>
       </c>
       <c r="I9">
-        <v>0.1905955623590889</v>
+        <v>0.02998384987988767</v>
       </c>
       <c r="J9">
-        <v>-0.8971459746756018</v>
+        <v>-0.6643444950370576</v>
       </c>
       <c r="K9">
-        <v>0.1503253976712387</v>
+        <v>-0.02904121441599773</v>
       </c>
       <c r="L9">
-        <v>-0.3524832053302394</v>
+        <v>-0.3477484896244957</v>
       </c>
       <c r="M9">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3634,28 +3634,28 @@
         <v>69</v>
       </c>
       <c r="F10">
-        <v>0.3040259186483687</v>
+        <v>0.2557294081405024</v>
       </c>
       <c r="G10">
-        <v>0.2866541318793874</v>
+        <v>0.1639433131519246</v>
       </c>
       <c r="H10">
-        <v>1.060601906049939</v>
+        <v>1.559864829030998</v>
       </c>
       <c r="I10">
-        <v>0.2888708559846507</v>
+        <v>0.1187918274297053</v>
       </c>
       <c r="J10">
-        <v>-0.3605092390815969</v>
+        <v>-0.03714608866042494</v>
       </c>
       <c r="K10">
-        <v>0.7684928986254855</v>
+        <v>0.6202842930391546</v>
       </c>
       <c r="L10">
-        <v>0.3040259194592988</v>
+        <v>0.2557294080923755</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3675,28 +3675,28 @@
         <v>70</v>
       </c>
       <c r="F11">
-        <v>-0.337775511713833</v>
+        <v>-0.3245311355015574</v>
       </c>
       <c r="G11">
-        <v>0.1962917397268776</v>
+        <v>0.1812523288585852</v>
       </c>
       <c r="H11">
-        <v>-1.720783116924928</v>
+        <v>-1.790493603835346</v>
       </c>
       <c r="I11">
-        <v>0.08529018716125103</v>
+        <v>0.07337459458582174</v>
       </c>
       <c r="J11">
-        <v>-0.7491897117662188</v>
+        <v>-0.6841567618097224</v>
       </c>
       <c r="K11">
-        <v>0.0214821613523745</v>
+        <v>0.02438678300874348</v>
       </c>
       <c r="L11">
-        <v>-0.3377755140482234</v>
+        <v>-0.3245311362204709</v>
       </c>
       <c r="M11">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3716,28 +3716,28 @@
         <v>71</v>
       </c>
       <c r="F12">
-        <v>0.05580207620268011</v>
+        <v>0.0007077890593673453</v>
       </c>
       <c r="G12">
-        <v>0.1761413225872891</v>
+        <v>0.1555890566911626</v>
       </c>
       <c r="H12">
-        <v>0.3168028681914016</v>
+        <v>0.004549092811663967</v>
       </c>
       <c r="I12">
-        <v>0.7513931877291673</v>
+        <v>0.9963703615986896</v>
       </c>
       <c r="J12">
-        <v>-0.2702414116657186</v>
+        <v>-0.3035751553389844</v>
       </c>
       <c r="K12">
-        <v>0.4199865404937983</v>
+        <v>0.3131102935131445</v>
       </c>
       <c r="L12">
-        <v>0.05580207601303086</v>
+        <v>0.0007077890575587728</v>
       </c>
       <c r="M12">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3757,28 +3757,28 @@
         <v>72</v>
       </c>
       <c r="F13">
-        <v>0.1784192569386154</v>
+        <v>0.1964712732507134</v>
       </c>
       <c r="G13">
-        <v>0.1809081601837636</v>
+        <v>0.1573346352956798</v>
       </c>
       <c r="H13">
-        <v>0.9862421725884556</v>
+        <v>1.24874775907723</v>
       </c>
       <c r="I13">
-        <v>0.3240142890373685</v>
+        <v>0.2117573467360649</v>
       </c>
       <c r="J13">
-        <v>-0.2006791689329991</v>
+        <v>-0.1216265668322567</v>
       </c>
       <c r="K13">
-        <v>0.5213406208161808</v>
+        <v>0.5035004185065705</v>
       </c>
       <c r="L13">
-        <v>0.1784192579667831</v>
+        <v>0.1964712734963969</v>
       </c>
       <c r="M13">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3798,28 +3798,28 @@
         <v>73</v>
       </c>
       <c r="F14">
-        <v>0.4182570101210575</v>
+        <v>0.2806557083430881</v>
       </c>
       <c r="G14">
-        <v>0.2031388676682258</v>
+        <v>0.1847626079973668</v>
       </c>
       <c r="H14">
-        <v>2.058970865212121</v>
+        <v>1.519007072833091</v>
       </c>
       <c r="I14">
-        <v>0.03949702957415435</v>
+        <v>0.1287607156730062</v>
       </c>
       <c r="J14">
-        <v>0.01261489650859279</v>
+        <v>-0.06368810243726497</v>
       </c>
       <c r="K14">
-        <v>0.8318209779059474</v>
+        <v>0.6658388995096048</v>
       </c>
       <c r="L14">
-        <v>0.418257008235048</v>
+        <v>0.2806557087128772</v>
       </c>
       <c r="M14">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3839,28 +3839,28 @@
         <v>117</v>
       </c>
       <c r="F15">
-        <v>0.1802004184875507</v>
+        <v>-0.05927860582183143</v>
       </c>
       <c r="G15">
-        <v>0.2826088094856761</v>
+        <v>0.18288128099078</v>
       </c>
       <c r="H15">
-        <v>0.6376319931975936</v>
+        <v>-0.3241370877362783</v>
       </c>
       <c r="I15">
-        <v>0.5237132644143143</v>
+        <v>0.7458342494264176</v>
       </c>
       <c r="J15">
-        <v>-0.3979528944355643</v>
+        <v>-0.3819271669524764</v>
       </c>
       <c r="K15">
-        <v>0.7451123796750988</v>
+        <v>0.354353290413883</v>
       </c>
       <c r="L15">
-        <v>0.1802004189682004</v>
+        <v>-0.05927860581067551</v>
       </c>
       <c r="M15">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3877,28 +3877,28 @@
         <v>62</v>
       </c>
       <c r="F16">
-        <v>-0.1843012964449261</v>
+        <v>-0.1635426724946745</v>
       </c>
       <c r="G16">
-        <v>0.1316641768416178</v>
+        <v>0.105557642126149</v>
       </c>
       <c r="H16">
-        <v>-1.399783151848713</v>
+        <v>-1.549321007940184</v>
       </c>
       <c r="I16">
-        <v>0.1615782645731845</v>
+        <v>0.1213045720968904</v>
       </c>
       <c r="J16">
-        <v>-0.4411336608925669</v>
+        <v>-0.3697540420924408</v>
       </c>
       <c r="K16">
-        <v>0.07416283281113555</v>
+        <v>0.04672015132886229</v>
       </c>
       <c r="L16">
-        <v>-0.2035492952400708</v>
+        <v>-0.1925777704988478</v>
       </c>
       <c r="M16">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3915,28 +3915,28 @@
         <v>64</v>
       </c>
       <c r="F17">
-        <v>-0.05969688878517659</v>
+        <v>-0.006460645124005783</v>
       </c>
       <c r="G17">
-        <v>0.1648272140717967</v>
+        <v>0.1450671483978294</v>
       </c>
       <c r="H17">
-        <v>-0.3621785948476529</v>
+        <v>-0.0445355491946959</v>
       </c>
       <c r="I17">
-        <v>0.7172185741341308</v>
+        <v>0.9644775159174517</v>
       </c>
       <c r="J17">
-        <v>-0.3737570348176256</v>
+        <v>-0.2943037380468839</v>
       </c>
       <c r="K17">
-        <v>0.2716175755775743</v>
+        <v>0.2641030363021947</v>
       </c>
       <c r="L17">
-        <v>-0.06441153993340383</v>
+        <v>-0.007290845274692767</v>
       </c>
       <c r="M17">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3953,28 +3953,28 @@
         <v>66</v>
       </c>
       <c r="F18">
-        <v>0.2819150239530773</v>
+        <v>0.2759791084860694</v>
       </c>
       <c r="G18">
-        <v>0.121923110967538</v>
+        <v>0.1073342405738751</v>
       </c>
       <c r="H18">
-        <v>2.31223614387708</v>
+        <v>2.571212196690589</v>
       </c>
       <c r="I18">
-        <v>0.02076467348687472</v>
+        <v>0.01013432103027356</v>
       </c>
       <c r="J18">
-        <v>0.0208630032730615</v>
+        <v>0.05161577678204975</v>
       </c>
       <c r="K18">
-        <v>0.4965322419512202</v>
+        <v>0.4669988840318754</v>
       </c>
       <c r="L18">
-        <v>0.3170885655399893</v>
+        <v>0.3256406574235451</v>
       </c>
       <c r="M18">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -3991,28 +3991,28 @@
         <v>64</v>
       </c>
       <c r="F19">
-        <v>-0.05310272364602901</v>
+        <v>-0.06586964039818435</v>
       </c>
       <c r="G19">
-        <v>0.1483594949713934</v>
+        <v>0.1276628806395304</v>
       </c>
       <c r="H19">
-        <v>-0.3579327609349726</v>
+        <v>-0.5159654871346218</v>
       </c>
       <c r="I19">
-        <v>0.7203936330690226</v>
+        <v>0.6058785142774694</v>
       </c>
       <c r="J19">
-        <v>-0.3448435436500421</v>
+        <v>-0.3146280912783115</v>
       </c>
       <c r="K19">
-        <v>0.2381619707239643</v>
+        <v>0.1812465109534476</v>
       </c>
       <c r="L19">
-        <v>-0.05870395098821798</v>
+        <v>-0.07420671927122297</v>
       </c>
       <c r="M19">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4029,28 +4029,28 @@
         <v>66</v>
       </c>
       <c r="F20">
-        <v>-0.1932549987353026</v>
+        <v>-0.1803002906594294</v>
       </c>
       <c r="G20">
-        <v>0.1101521598848542</v>
+        <v>0.1017087821209972</v>
       </c>
       <c r="H20">
-        <v>-1.754436762178051</v>
+        <v>-1.772711135651356</v>
       </c>
       <c r="I20">
-        <v>0.07935569678195509</v>
+        <v>0.0762765849338094</v>
       </c>
       <c r="J20">
-        <v>-0.3890140508617886</v>
+        <v>-0.3718296508372395</v>
       </c>
       <c r="K20">
-        <v>0.03618296233374526</v>
+        <v>0.02439107715430433</v>
       </c>
       <c r="L20">
-        <v>-0.2227058611557943</v>
+        <v>-0.2123805719110513</v>
       </c>
       <c r="M20">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4067,28 +4067,28 @@
         <v>66</v>
       </c>
       <c r="F21">
-        <v>0.3211851693178581</v>
+        <v>0.3805574212275756</v>
       </c>
       <c r="G21">
-        <v>0.1241261925524224</v>
+        <v>0.1127872797840461</v>
       </c>
       <c r="H21">
-        <v>2.587569655632605</v>
+        <v>3.374116495727438</v>
       </c>
       <c r="I21">
-        <v>0.009665565125861919</v>
+        <v>0.0007405302133847158</v>
       </c>
       <c r="J21">
-        <v>0.05889303387819284</v>
+        <v>0.1383117573449135</v>
       </c>
       <c r="K21">
-        <v>0.5476803427256073</v>
+        <v>0.5708967864817388</v>
       </c>
       <c r="L21">
-        <v>0.3615989544845027</v>
+        <v>0.4296012001229268</v>
       </c>
       <c r="M21">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4105,28 +4105,28 @@
         <v>112</v>
       </c>
       <c r="F22">
-        <v>-0.7572881932320493</v>
+        <v>-0.3730383107118532</v>
       </c>
       <c r="G22">
-        <v>0.1029208282252121</v>
+        <v>0.132246299279962</v>
       </c>
       <c r="H22">
-        <v>-7.357968316917792</v>
+        <v>-2.820784496374758</v>
       </c>
       <c r="I22">
-        <v>1.867395127419513E-13</v>
+        <v>0.004790637353986549</v>
       </c>
       <c r="J22">
-        <v>-0.9451812892714206</v>
+        <v>-0.6160145482321007</v>
       </c>
       <c r="K22">
-        <v>-0.5508607075589825</v>
+        <v>-0.09428044822750033</v>
       </c>
       <c r="L22">
-        <v>-0.7789249987529647</v>
+        <v>-0.3817136202632916</v>
       </c>
       <c r="M22">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4146,28 +4146,28 @@
         <v>78</v>
       </c>
       <c r="F23">
-        <v>-0.1024346028594284</v>
+        <v>-0.1248923797632825</v>
       </c>
       <c r="G23">
-        <v>0.1208271257268132</v>
+        <v>0.09284936601481082</v>
       </c>
       <c r="H23">
-        <v>-0.8477781975136131</v>
+        <v>-1.345107512563525</v>
       </c>
       <c r="I23">
-        <v>0.3965615073940287</v>
+        <v>0.1785905174966602</v>
       </c>
       <c r="J23">
-        <v>-0.4157216898743987</v>
+        <v>-0.3510803620110109</v>
       </c>
       <c r="K23">
-        <v>0.0495474335167362</v>
+        <v>0.007580338250847207</v>
       </c>
       <c r="L23">
-        <v>-0.1024346031326528</v>
+        <v>-0.1248923797397784</v>
       </c>
       <c r="M23">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4187,28 +4187,28 @@
         <v>81</v>
       </c>
       <c r="F24">
-        <v>0.002895260247222891</v>
+        <v>-0.000151294368931996</v>
       </c>
       <c r="G24">
-        <v>0.06615501074717887</v>
+        <v>0.04707703017682466</v>
       </c>
       <c r="H24">
-        <v>0.04376479142732747</v>
+        <v>-0.003213761963397514</v>
       </c>
       <c r="I24">
-        <v>0.9650918925500762</v>
+        <v>0.9974357933612783</v>
       </c>
       <c r="J24">
-        <v>-0.1195538222047855</v>
+        <v>-0.09454407361891951</v>
       </c>
       <c r="K24">
-        <v>0.162731656565618</v>
+        <v>0.1110387695422881</v>
       </c>
       <c r="L24">
-        <v>0.002895260254945435</v>
+        <v>-0.0001512943689035233</v>
       </c>
       <c r="M24">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -4228,28 +4228,28 @@
         <v>84</v>
       </c>
       <c r="F25">
-        <v>0.03088537635110638</v>
+        <v>0.0292215526844712</v>
       </c>
       <c r="G25">
-        <v>0.0932612547100491</v>
+        <v>0.0470662348962387</v>
       </c>
       <c r="H25">
-        <v>0.3311704999801854</v>
+        <v>0.6208602143105871</v>
       </c>
       <c r="I25">
-        <v>0.7405157017422508</v>
+        <v>0.534691600496402</v>
       </c>
       <c r="J25">
-        <v>-0.1237910610254593</v>
+        <v>-0.04177639816559586</v>
       </c>
       <c r="K25">
-        <v>0.2685277764934617</v>
+        <v>0.1438963809416152</v>
       </c>
       <c r="L25">
-        <v>0.03088537643348712</v>
+        <v>0.02922155267897185</v>
       </c>
       <c r="M25">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -4269,28 +4269,28 @@
         <v>87</v>
       </c>
       <c r="F26">
-        <v>-0.0005073884597818456</v>
+        <v>0.01117159507005304</v>
       </c>
       <c r="G26">
-        <v>0.1075237010252772</v>
+        <v>0.06618502551431758</v>
       </c>
       <c r="H26">
-        <v>-0.004718852261814965</v>
+        <v>0.1687933937207039</v>
       </c>
       <c r="I26">
-        <v>0.9962349146088083</v>
+        <v>0.8659591548134704</v>
       </c>
       <c r="J26">
-        <v>-0.2169194856811365</v>
+        <v>-0.1072152439713106</v>
       </c>
       <c r="K26">
-        <v>0.2291588785226428</v>
+        <v>0.1745690259035574</v>
       </c>
       <c r="L26">
-        <v>-0.0005073884611352059</v>
+        <v>0.01117159506795061</v>
       </c>
       <c r="M26">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -4310,28 +4310,28 @@
         <v>88</v>
       </c>
       <c r="F27">
-        <v>-0.06916135472088095</v>
+        <v>-0.08465052637769024</v>
       </c>
       <c r="G27">
-        <v>0.1850329423817499</v>
+        <v>0.1049222881831039</v>
       </c>
       <c r="H27">
-        <v>-0.3737786030456728</v>
+        <v>-0.8067926066381946</v>
       </c>
       <c r="I27">
-        <v>0.7085690398450974</v>
+        <v>0.4197859794160068</v>
       </c>
       <c r="J27">
-        <v>-0.4481453697910466</v>
+        <v>-0.2881529206191223</v>
       </c>
       <c r="K27">
-        <v>0.2867003363101536</v>
+        <v>0.1204246471557724</v>
       </c>
       <c r="L27">
-        <v>-0.06916135490535542</v>
+        <v>-0.08465052636175946</v>
       </c>
       <c r="M27">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4351,28 +4351,28 @@
         <v>90</v>
       </c>
       <c r="F28">
-        <v>0.2348645639274878</v>
+        <v>0.1710788817628121</v>
       </c>
       <c r="G28">
-        <v>0.3169399567841402</v>
+        <v>0.1640004506157233</v>
       </c>
       <c r="H28">
-        <v>0.7410380385943199</v>
+        <v>1.043161046939283</v>
       </c>
       <c r="I28">
-        <v>0.458670376722278</v>
+        <v>0.2968737109955824</v>
       </c>
       <c r="J28">
-        <v>-0.4646755585646112</v>
+        <v>-0.118134655323089</v>
       </c>
       <c r="K28">
-        <v>0.7867021128651055</v>
+        <v>0.5255319202004352</v>
       </c>
       <c r="L28">
-        <v>0.2348645645539434</v>
+        <v>0.171078881730616</v>
       </c>
       <c r="M28">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4392,28 +4392,28 @@
         <v>94</v>
       </c>
       <c r="F29">
-        <v>-0.1053298631066513</v>
+        <v>-0.1247410853943505</v>
       </c>
       <c r="G29">
-        <v>0.1377877619800272</v>
+        <v>0.1130945499013559</v>
       </c>
       <c r="H29">
-        <v>-0.7644355463289926</v>
+        <v>-1.102980519425145</v>
       </c>
       <c r="I29">
-        <v>0.4446077325532496</v>
+        <v>0.270035625013112</v>
       </c>
       <c r="J29">
-        <v>-0.4376924601224617</v>
+        <v>-0.3966603135595696</v>
       </c>
       <c r="K29">
-        <v>0.10394963329537</v>
+        <v>0.04523358937906431</v>
       </c>
       <c r="L29">
-        <v>-0.1053298633875982</v>
+        <v>-0.1247410853708749</v>
       </c>
       <c r="M29">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4433,28 +4433,28 @@
         <v>97</v>
       </c>
       <c r="F30">
-        <v>-0.1333199792105348</v>
+        <v>-0.1541139324477537</v>
       </c>
       <c r="G30">
-        <v>0.1365856211965054</v>
+        <v>0.1028130175984399</v>
       </c>
       <c r="H30">
-        <v>-0.9760908801573456</v>
+        <v>-1.498972951554456</v>
       </c>
       <c r="I30">
-        <v>0.3290194303236502</v>
+        <v>0.1338806492150439</v>
       </c>
       <c r="J30">
-        <v>-0.4664394305478671</v>
+        <v>-0.3920655871952676</v>
       </c>
       <c r="K30">
-        <v>0.08278392531226027</v>
+        <v>0.007771651111342826</v>
       </c>
       <c r="L30">
-        <v>-0.1333199795661399</v>
+        <v>-0.1541139324187503</v>
       </c>
       <c r="M30">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4474,28 +4474,28 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>-0.1019272143996465</v>
+        <v>-0.1360639748333355</v>
       </c>
       <c r="G31">
-        <v>0.185840403962908</v>
+        <v>0.1324923679587742</v>
       </c>
       <c r="H31">
-        <v>-0.5484663841991554</v>
+        <v>-1.026957076317578</v>
       </c>
       <c r="I31">
-        <v>0.5833717051464871</v>
+        <v>0.304440676353235</v>
       </c>
       <c r="J31">
-        <v>-0.5458432890825459</v>
+        <v>-0.4680388739701048</v>
       </c>
       <c r="K31">
-        <v>0.1980592230770578</v>
+        <v>0.05684875051298366</v>
       </c>
       <c r="L31">
-        <v>-0.1019272146715176</v>
+        <v>-0.136063974807729</v>
       </c>
       <c r="M31">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4515,28 +4515,28 @@
         <v>103</v>
       </c>
       <c r="F32">
-        <v>-0.02799011610388349</v>
+        <v>-0.02937284705340319</v>
       </c>
       <c r="G32">
-        <v>0.1181422609092905</v>
+        <v>0.07093233719154793</v>
       </c>
       <c r="H32">
-        <v>-0.2369187443041595</v>
+        <v>-0.4140967042166371</v>
       </c>
       <c r="I32">
-        <v>0.8127198280670509</v>
+        <v>0.6788032863948477</v>
       </c>
       <c r="J32">
-        <v>-0.2907239360894323</v>
+        <v>-0.1922456170449745</v>
       </c>
       <c r="K32">
-        <v>0.2151074556709852</v>
+        <v>0.09958573990206052</v>
       </c>
       <c r="L32">
-        <v>-0.02799011617854169</v>
+        <v>-0.02937284704787537</v>
       </c>
       <c r="M32">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4556,28 +4556,28 @@
         <v>106</v>
       </c>
       <c r="F33">
-        <v>0.003402648707004736</v>
+        <v>-0.01132288943898503</v>
       </c>
       <c r="G33">
-        <v>0.1332485513865822</v>
+        <v>0.08507094748777855</v>
       </c>
       <c r="H33">
-        <v>0.02553610280634822</v>
+        <v>-0.1330993690955623</v>
       </c>
       <c r="I33">
-        <v>0.9796273519937859</v>
+        <v>0.8941147940969714</v>
       </c>
       <c r="J33">
-        <v>-0.2673562656654493</v>
+        <v>-0.2166289697462877</v>
       </c>
       <c r="K33">
-        <v>0.2800695484506508</v>
+        <v>0.1389957758025321</v>
       </c>
       <c r="L33">
-        <v>0.003402648716080641</v>
+        <v>-0.01132288943685413</v>
       </c>
       <c r="M33">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4597,28 +4597,28 @@
         <v>109</v>
       </c>
       <c r="F34">
-        <v>0.03139276481088823</v>
+        <v>0.01804995761441816</v>
       </c>
       <c r="G34">
-        <v>0.1371533289515304</v>
+        <v>0.07442773636978554</v>
       </c>
       <c r="H34">
-        <v>0.2288880995515781</v>
+        <v>0.2425165468520908</v>
       </c>
       <c r="I34">
-        <v>0.8189558902435499</v>
+        <v>0.8083799369458449</v>
       </c>
       <c r="J34">
-        <v>-0.2353100674028455</v>
+        <v>-0.155372940583004</v>
       </c>
       <c r="K34">
-        <v>0.3287314775261821</v>
+        <v>0.1559628442015371</v>
       </c>
       <c r="L34">
-        <v>0.03139276489462233</v>
+        <v>0.01804995761102125</v>
       </c>
       <c r="M34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4659,19 +4659,19 @@
         <v>119</v>
       </c>
       <c r="B2">
-        <v>-0.0167082426418953</v>
+        <v>-0.07831555740649336</v>
       </c>
       <c r="C2">
-        <v>0.1143333204148515</v>
+        <v>0.149555211787737</v>
       </c>
       <c r="D2">
-        <v>-0.3159712444087429</v>
+        <v>-0.4794234011111195</v>
       </c>
       <c r="E2">
-        <v>0.1454004932605414</v>
+        <v>0.1042351885293506</v>
       </c>
       <c r="F2">
-        <v>0.8838138305933807</v>
+        <v>0.6005174826449968</v>
       </c>
       <c r="G2" t="s">
         <v>120</v>
@@ -4682,19 +4682,19 @@
         <v>121</v>
       </c>
       <c r="B3">
-        <v>-0.0007874806728245196</v>
+        <v>0.01898449596889564</v>
       </c>
       <c r="C3">
-        <v>0.09705379576997995</v>
+        <v>0.08263457718978627</v>
       </c>
       <c r="D3">
-        <v>-0.1971391315766076</v>
+        <v>-0.06181139170170001</v>
       </c>
       <c r="E3">
-        <v>0.1886540391002247</v>
+        <v>0.2437294403969917</v>
       </c>
       <c r="F3">
-        <v>0.9935261493724472</v>
+        <v>0.8182935453735276</v>
       </c>
       <c r="G3" t="s">
         <v>122</v>
@@ -4705,19 +4705,19 @@
         <v>123</v>
       </c>
       <c r="B4">
-        <v>0.06269613150968362</v>
+        <v>0.04695072176694131</v>
       </c>
       <c r="C4">
-        <v>0.2289697585608703</v>
+        <v>0.1163728175601816</v>
       </c>
       <c r="D4">
-        <v>-0.4676535681633284</v>
+        <v>-0.1735467238923001</v>
       </c>
       <c r="E4">
-        <v>0.4784711678608465</v>
+        <v>0.2830720049320564</v>
       </c>
       <c r="F4">
-        <v>0.7842241874788201</v>
+        <v>0.6866165244730291</v>
       </c>
       <c r="G4" t="s">
         <v>124</v>
@@ -4728,19 +4728,19 @@
         <v>125</v>
       </c>
       <c r="B5">
-        <v>-0.01444555127856032</v>
+        <v>0.001803443647148764</v>
       </c>
       <c r="C5">
-        <v>0.08255788622199176</v>
+        <v>0.05711258298712613</v>
       </c>
       <c r="D5">
-        <v>-0.2323273047340109</v>
+        <v>-0.1235036146131318</v>
       </c>
       <c r="E5">
-        <v>0.1039003122454961</v>
+        <v>0.1158970467088345</v>
       </c>
       <c r="F5">
-        <v>0.8610994190913419</v>
+        <v>0.9748093909700284</v>
       </c>
       <c r="G5" t="s">
         <v>126</v>
@@ -4751,19 +4751,19 @@
         <v>127</v>
       </c>
       <c r="B6">
-        <v>-0.2002889617983713</v>
+        <v>-0.1218455476226812</v>
       </c>
       <c r="C6">
-        <v>0.3278442171099974</v>
+        <v>0.1694681665210635</v>
       </c>
       <c r="D6">
-        <v>-0.8265079684386275</v>
+        <v>-0.5625764725920227</v>
       </c>
       <c r="E6">
-        <v>0.3637536788384895</v>
+        <v>0.08264185808517129</v>
       </c>
       <c r="F6">
-        <v>0.5412477521695696</v>
+        <v>0.4721484243108252</v>
       </c>
       <c r="G6" t="s">
         <v>128</v>
@@ -4774,19 +4774,19 @@
         <v>129</v>
       </c>
       <c r="B7">
-        <v>-0.002814924304480512</v>
+        <v>-0.02800637921812778</v>
       </c>
       <c r="C7">
-        <v>0.1736844271454552</v>
+        <v>0.1484526185909339</v>
       </c>
       <c r="D7">
-        <v>-0.3655370557923487</v>
+        <v>-0.2905909506699506</v>
       </c>
       <c r="E7">
-        <v>0.2614418846883756</v>
+        <v>0.3129419029204592</v>
       </c>
       <c r="F7">
-        <v>0.9870691554941227</v>
+        <v>0.8503629565447777</v>
       </c>
       <c r="G7" t="s">
         <v>130</v>
@@ -4797,19 +4797,19 @@
         <v>131</v>
       </c>
       <c r="B8">
-        <v>-0.04899746773819537</v>
+        <v>-0.04149075164789405</v>
       </c>
       <c r="C8">
-        <v>0.2081304986999939</v>
+        <v>0.1207708550809906</v>
       </c>
       <c r="D8">
-        <v>-0.5602863935954052</v>
+        <v>-0.3448315396019778</v>
       </c>
       <c r="E8">
-        <v>0.215024084290567</v>
+        <v>0.1450248334679962</v>
       </c>
       <c r="F8">
-        <v>0.813885054960191</v>
+        <v>0.7311852033770192</v>
       </c>
       <c r="G8" t="s">
         <v>132</v>
@@ -4820,19 +4820,19 @@
         <v>133</v>
       </c>
       <c r="B9">
-        <v>0.4336599635394644</v>
+        <v>0.1419378067255481</v>
       </c>
       <c r="C9">
-        <v>0.6353250509554537</v>
+        <v>0.3471694214847054</v>
       </c>
       <c r="D9">
-        <v>-0.6701501212140061</v>
+        <v>-0.3656517950487938</v>
       </c>
       <c r="E9">
-        <v>1.826916731940209</v>
+        <v>1.109866460059836</v>
       </c>
       <c r="F9">
-        <v>0.494872484154985</v>
+        <v>0.6826548414270766</v>
       </c>
       <c r="G9" t="s">
         <v>134</v>
@@ -4843,19 +4843,19 @@
         <v>135</v>
       </c>
       <c r="B10">
-        <v>0.183580719156476</v>
+        <v>0.04352999021618779</v>
       </c>
       <c r="C10">
-        <v>0.3484585438245418</v>
+        <v>0.2270000575755923</v>
       </c>
       <c r="D10">
-        <v>-0.4685052337354933</v>
+        <v>-0.413694769953868</v>
       </c>
       <c r="E10">
-        <v>0.8234660267353858</v>
+        <v>0.513923300270692</v>
       </c>
       <c r="F10">
-        <v>0.5983070547963201</v>
+        <v>0.8479286202362979</v>
       </c>
       <c r="G10" t="s">
         <v>136</v>
@@ -4866,19 +4866,19 @@
         <v>137</v>
       </c>
       <c r="B11">
-        <v>0.002027443631655993</v>
+        <v>0.04699087518702343</v>
       </c>
       <c r="C11">
-        <v>0.1983191032439596</v>
+        <v>0.1696776337298617</v>
       </c>
       <c r="D11">
-        <v>-0.3425271569179909</v>
+        <v>-0.300466499977135</v>
       </c>
       <c r="E11">
-        <v>0.4095548950057631</v>
+        <v>0.3981324973634797</v>
       </c>
       <c r="F11">
-        <v>0.9918432578211416</v>
+        <v>0.7818245879631207</v>
       </c>
       <c r="G11" t="s">
         <v>138</v>
@@ -4889,19 +4889,19 @@
         <v>139</v>
       </c>
       <c r="B12">
-        <v>0.111693599247879</v>
+        <v>0.08844147341483535</v>
       </c>
       <c r="C12">
-        <v>0.3114399509514737</v>
+        <v>0.1668044078479344</v>
       </c>
       <c r="D12">
-        <v>-0.49315255188049</v>
+        <v>-0.2058284188711197</v>
       </c>
       <c r="E12">
-        <v>0.7741405762694217</v>
+        <v>0.4617865627742386</v>
       </c>
       <c r="F12">
-        <v>0.7198673614117492</v>
+        <v>0.595965888219296</v>
       </c>
       <c r="G12" t="s">
         <v>140</v>
@@ -4912,19 +4912,19 @@
         <v>141</v>
       </c>
       <c r="B13">
-        <v>-0.4481055148180247</v>
+        <v>-0.1401343630783994</v>
       </c>
       <c r="C13">
-        <v>0.6397203817065776</v>
+        <v>0.3524094942117129</v>
       </c>
       <c r="D13">
-        <v>-1.833600436954276</v>
+        <v>-1.103300646962876</v>
       </c>
       <c r="E13">
-        <v>0.6591146666120873</v>
+        <v>0.3751865214664222</v>
       </c>
       <c r="F13">
-        <v>0.4836332689499183</v>
+        <v>0.6908908602158728</v>
       </c>
       <c r="G13" t="s">
         <v>142</v>
@@ -4935,19 +4935,19 @@
         <v>143</v>
       </c>
       <c r="B14">
-        <v>1.937644946084428</v>
+        <v>-0.1414116592809892</v>
       </c>
       <c r="C14">
-        <v>0.6684774381153258</v>
+        <v>0.5398750820951403</v>
       </c>
       <c r="D14">
-        <v>0.6816611268433576</v>
+        <v>-0.8402841117375773</v>
       </c>
       <c r="E14">
-        <v>3.29724184182137</v>
+        <v>1.182351178869352</v>
       </c>
       <c r="F14">
-        <v>0.003748394730827442</v>
+        <v>0.7933722983788922</v>
       </c>
       <c r="G14" t="s">
         <v>144</v>
@@ -5021,28 +5021,28 @@
         <v>78</v>
       </c>
       <c r="F2">
-        <v>-0.01379512085308073</v>
+        <v>-0.08966941234656185</v>
       </c>
       <c r="G2">
-        <v>0.09706123988341031</v>
+        <v>0.1644596375445589</v>
       </c>
       <c r="H2">
-        <v>-0.142128009797231</v>
+        <v>-0.5452365923053109</v>
       </c>
       <c r="I2">
-        <v>0.8869788941369345</v>
+        <v>0.5855908075105269</v>
       </c>
       <c r="J2">
-        <v>-0.2827289224971024</v>
+        <v>-0.5411689399528838</v>
       </c>
       <c r="K2">
-        <v>0.123308326752328</v>
+        <v>0.1119226776907945</v>
       </c>
       <c r="L2">
-        <v>-0.01379512079794074</v>
+        <v>-0.08966941237589242</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5062,28 +5062,28 @@
         <v>81</v>
       </c>
       <c r="F3">
-        <v>-0.0006501812653554213</v>
+        <v>0.02173678709059068</v>
       </c>
       <c r="G3">
-        <v>0.07851450477465306</v>
+        <v>0.08880989547307132</v>
       </c>
       <c r="H3">
-        <v>-0.008281033768493184</v>
+        <v>0.2447563638579177</v>
       </c>
       <c r="I3">
-        <v>0.993392766524464</v>
+        <v>0.8066450829488945</v>
       </c>
       <c r="J3">
-        <v>-0.162549770670685</v>
+        <v>-0.07847473031028127</v>
       </c>
       <c r="K3">
-        <v>0.1684305434778464</v>
+        <v>0.260876952877951</v>
       </c>
       <c r="L3">
-        <v>-0.0006501812627566046</v>
+        <v>0.02173678709770072</v>
       </c>
       <c r="M3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5103,28 +5103,28 @@
         <v>84</v>
       </c>
       <c r="F4">
-        <v>0.05176491103594025</v>
+        <v>0.05375743683002785</v>
       </c>
       <c r="G4">
-        <v>0.1877456151309055</v>
+        <v>0.1299695983096516</v>
       </c>
       <c r="H4">
-        <v>0.2757183490003066</v>
+        <v>0.4136154726119193</v>
       </c>
       <c r="I4">
-        <v>0.7827644012514849</v>
+        <v>0.6791557399549943</v>
       </c>
       <c r="J4">
-        <v>-0.3975469004468558</v>
+        <v>-0.1893481627692</v>
       </c>
       <c r="K4">
-        <v>0.384123698038462</v>
+        <v>0.3385900792271178</v>
       </c>
       <c r="L4">
-        <v>0.05176491082903253</v>
+        <v>0.05375743684761174</v>
       </c>
       <c r="M4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5144,28 +5144,28 @@
         <v>87</v>
       </c>
       <c r="F5">
-        <v>-0.01192693441499119</v>
+        <v>0.002064899202602467</v>
       </c>
       <c r="G5">
-        <v>0.06816411204130765</v>
+        <v>0.06504702767566659</v>
       </c>
       <c r="H5">
-        <v>-0.1749738103793303</v>
+        <v>0.03174471265464025</v>
       </c>
       <c r="I5">
-        <v>0.8611002123886407</v>
+        <v>0.9746756372969105</v>
       </c>
       <c r="J5">
-        <v>-0.1936142801163783</v>
+        <v>-0.1483840499824843</v>
       </c>
       <c r="K5">
-        <v>0.08735538863259122</v>
+        <v>0.1353272578484186</v>
       </c>
       <c r="L5">
-        <v>-0.01192693436731845</v>
+        <v>0.00206489920327789</v>
       </c>
       <c r="M5">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5185,28 +5185,28 @@
         <v>88</v>
       </c>
       <c r="F6">
-        <v>0.0253926745025129</v>
+        <v>-0.01211028922334085</v>
       </c>
       <c r="G6">
-        <v>0.2474037228179007</v>
+        <v>0.2050155203246768</v>
       </c>
       <c r="H6">
-        <v>0.1026365901583581</v>
+        <v>-0.05907010944421259</v>
       </c>
       <c r="I6">
-        <v>0.9182514014322076</v>
+        <v>0.9528962662634057</v>
       </c>
       <c r="J6">
-        <v>-0.5843026102505494</v>
+        <v>-0.4276890583758312</v>
       </c>
       <c r="K6">
-        <v>0.4150129950884399</v>
+        <v>0.3945098423560491</v>
       </c>
       <c r="L6">
-        <v>0.02539267440101674</v>
+        <v>-0.01211028922730207</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5226,28 +5226,28 @@
         <v>90</v>
       </c>
       <c r="F7">
-        <v>0.4692488926256184</v>
+        <v>0.162163592138079</v>
       </c>
       <c r="G7">
-        <v>0.2351990864484656</v>
+        <v>0.2605522124944769</v>
       </c>
       <c r="H7">
-        <v>1.99511358530908</v>
+        <v>0.6223842453132746</v>
       </c>
       <c r="I7">
-        <v>0.04603049299452211</v>
+        <v>0.5336892374190216</v>
       </c>
       <c r="J7">
-        <v>-0.009420621797506447</v>
+        <v>-0.2245066739369579</v>
       </c>
       <c r="K7">
-        <v>0.9064294185865254</v>
+        <v>0.7869045106666488</v>
       </c>
       <c r="L7">
-        <v>0.46924889075</v>
+        <v>0.1621635921911222</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5267,28 +5267,28 @@
         <v>94</v>
       </c>
       <c r="F8">
-        <v>-0.01314493958772531</v>
+        <v>-0.1114061994371525</v>
       </c>
       <c r="G8">
-        <v>0.1233483180399397</v>
+        <v>0.2047064069134752</v>
       </c>
       <c r="H8">
-        <v>-0.1065676435366474</v>
+        <v>-0.5442242923263336</v>
       </c>
       <c r="I8">
-        <v>0.9151319890836882</v>
+        <v>0.5862871371845571</v>
       </c>
       <c r="J8">
-        <v>-0.3160759881729552</v>
+        <v>-0.706300316364833</v>
       </c>
       <c r="K8">
-        <v>0.1737600537256887</v>
+        <v>0.1222560441969727</v>
       </c>
       <c r="L8">
-        <v>-0.01314493953518413</v>
+        <v>-0.1114061994735931</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5308,28 +5308,28 @@
         <v>97</v>
       </c>
       <c r="F9">
-        <v>-0.06556003188902099</v>
+        <v>-0.1434268491765897</v>
       </c>
       <c r="G9">
-        <v>0.2037736011026745</v>
+        <v>0.2155244504041514</v>
       </c>
       <c r="H9">
-        <v>-0.3217297605492457</v>
+        <v>-0.6654783200125819</v>
       </c>
       <c r="I9">
-        <v>0.7476574299455061</v>
+        <v>0.5057446056742996</v>
       </c>
       <c r="J9">
-        <v>-0.4258980642091154</v>
+        <v>-0.6555172953164511</v>
       </c>
       <c r="K9">
-        <v>0.4097582320284656</v>
+        <v>0.2497202110673001</v>
       </c>
       <c r="L9">
-        <v>-0.06556003162697327</v>
+        <v>-0.1434268492235042</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5349,28 +5349,28 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>-0.001868186438089543</v>
+        <v>-0.09173431154916432</v>
       </c>
       <c r="G10">
-        <v>0.1217971993130217</v>
+        <v>0.1890850423705143</v>
       </c>
       <c r="H10">
-        <v>-0.01533850079169932</v>
+        <v>-0.4851484305639042</v>
       </c>
       <c r="I10">
-        <v>0.9877621269009202</v>
+        <v>0.6275710598340589</v>
       </c>
       <c r="J10">
-        <v>-0.293395653822604</v>
+        <v>-0.5892180253508644</v>
       </c>
       <c r="K10">
-        <v>0.2334253384104693</v>
+        <v>0.1550550752557589</v>
       </c>
       <c r="L10">
-        <v>-0.001868186430622282</v>
+        <v>-0.09173431157917031</v>
       </c>
       <c r="M10">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5390,28 +5390,28 @@
         <v>103</v>
       </c>
       <c r="F11">
-        <v>-0.05241509230129567</v>
+        <v>-0.03202064973943716</v>
       </c>
       <c r="G11">
-        <v>0.2000648953959787</v>
+        <v>0.1553428627271248</v>
       </c>
       <c r="H11">
-        <v>-0.2619904516359706</v>
+        <v>-0.2061288763274861</v>
       </c>
       <c r="I11">
-        <v>0.793328803644934</v>
+        <v>0.8366902430394954</v>
       </c>
       <c r="J11">
-        <v>-0.3959486540344582</v>
+        <v>-0.3440177362752985</v>
       </c>
       <c r="K11">
-        <v>0.4347772473983176</v>
+        <v>0.2786650830156297</v>
       </c>
       <c r="L11">
-        <v>-0.05241509209178914</v>
+        <v>-0.03202064974991102</v>
       </c>
       <c r="M11">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5431,28 +5431,28 @@
         <v>106</v>
       </c>
       <c r="F12">
-        <v>0.01127675314963577</v>
+        <v>0.01967188788798822</v>
       </c>
       <c r="G12">
-        <v>0.1024077728907155</v>
+        <v>0.1106778133825401</v>
       </c>
       <c r="H12">
-        <v>0.1101161838727785</v>
+        <v>0.1777401205063159</v>
       </c>
       <c r="I12">
-        <v>0.9123172333359078</v>
+        <v>0.8589270752776186</v>
       </c>
       <c r="J12">
-        <v>-0.1747407030268678</v>
+        <v>-0.1401048143832075</v>
       </c>
       <c r="K12">
-        <v>0.2387831720577824</v>
+        <v>0.2913274068561475</v>
       </c>
       <c r="L12">
-        <v>0.01127675310456185</v>
+        <v>0.01967188789442283</v>
       </c>
       <c r="M12">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5472,28 +5472,28 @@
         <v>109</v>
       </c>
       <c r="F13">
-        <v>0.06369184545093144</v>
+        <v>0.05169253762742539</v>
       </c>
       <c r="G13">
-        <v>0.196534306072444</v>
+        <v>0.1473381379231265</v>
       </c>
       <c r="H13">
-        <v>0.3240749501893789</v>
+        <v>0.3508428866828486</v>
       </c>
       <c r="I13">
-        <v>0.7458812912334489</v>
+        <v>0.7257062208392773</v>
       </c>
       <c r="J13">
-        <v>-0.3901180448184062</v>
+        <v>-0.2253022944731676</v>
       </c>
       <c r="K13">
-        <v>0.4112308530897452</v>
+        <v>0.3791886104549344</v>
       </c>
       <c r="L13">
-        <v>0.06369184519635099</v>
+        <v>0.05169253764433385</v>
       </c>
       <c r="M13">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -5513,28 +5513,28 @@
         <v>78</v>
       </c>
       <c r="F14">
-        <v>-0.07551187097807646</v>
+        <v>-0.08564353363440193</v>
       </c>
       <c r="G14">
-        <v>0.1211085492931236</v>
+        <v>0.1231753885845921</v>
       </c>
       <c r="H14">
-        <v>-0.6235057014456695</v>
+        <v>-0.6952974503959877</v>
       </c>
       <c r="I14">
-        <v>0.5329522567714688</v>
+        <v>0.4868689117474621</v>
       </c>
       <c r="J14">
-        <v>-0.314547219644992</v>
+        <v>-0.3885211891534668</v>
       </c>
       <c r="K14">
-        <v>0.125316180866851</v>
+        <v>0.05422294683398064</v>
       </c>
       <c r="L14">
-        <v>-0.07551187129160697</v>
+        <v>-0.08564353362504375</v>
       </c>
       <c r="M14">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5554,28 +5554,28 @@
         <v>81</v>
       </c>
       <c r="F15">
-        <v>-0.001061267677396989</v>
+        <v>-0.01968529279357133</v>
       </c>
       <c r="G15">
-        <v>0.07152871240250074</v>
+        <v>0.1013759060035073</v>
       </c>
       <c r="H15">
-        <v>-0.01483694647577476</v>
+        <v>-0.1941811774573959</v>
       </c>
       <c r="I15">
-        <v>0.9881622637957528</v>
+        <v>0.8460340205710193</v>
       </c>
       <c r="J15">
-        <v>-0.1421081681523532</v>
+        <v>-0.2104817106114766</v>
       </c>
       <c r="K15">
-        <v>0.09549358632725466</v>
+        <v>0.2088106624030726</v>
       </c>
       <c r="L15">
-        <v>-0.001061267681803446</v>
+        <v>-0.01968529279142034</v>
       </c>
       <c r="M15">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5595,28 +5595,28 @@
         <v>84</v>
       </c>
       <c r="F16">
-        <v>-0.01847276270328368</v>
+        <v>-0.02916326984123241</v>
       </c>
       <c r="G16">
-        <v>0.07628457088996213</v>
+        <v>0.08627307773519942</v>
       </c>
       <c r="H16">
-        <v>-0.242155949594709</v>
+        <v>-0.3380344205494108</v>
       </c>
       <c r="I16">
-        <v>0.8086593264606803</v>
+        <v>0.7353372491156702</v>
       </c>
       <c r="J16">
-        <v>-0.2088823030289577</v>
+        <v>-0.2385999940261567</v>
       </c>
       <c r="K16">
-        <v>0.07836168568735258</v>
+        <v>0.1075636825620861</v>
       </c>
       <c r="L16">
-        <v>-0.01847276277998387</v>
+        <v>-0.02916326983804577</v>
       </c>
       <c r="M16">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5636,28 +5636,28 @@
         <v>87</v>
       </c>
       <c r="F17">
-        <v>0.1634961569865961</v>
+        <v>0.09976610193370891</v>
       </c>
       <c r="G17">
-        <v>0.2322581215606281</v>
+        <v>0.234080452387484</v>
       </c>
       <c r="H17">
-        <v>0.7039416141317472</v>
+        <v>0.4262043281109247</v>
       </c>
       <c r="I17">
-        <v>0.4814691345472721</v>
+        <v>0.6699589639854922</v>
       </c>
       <c r="J17">
-        <v>-0.2315461823200897</v>
+        <v>-0.2580126552397989</v>
       </c>
       <c r="K17">
-        <v>0.6613977789990788</v>
+        <v>0.7191682083783921</v>
       </c>
       <c r="L17">
-        <v>0.1634961576654434</v>
+        <v>0.09976610192280755</v>
       </c>
       <c r="M17">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5677,28 +5677,28 @@
         <v>88</v>
       </c>
       <c r="F18">
-        <v>0.06845025562783894</v>
+        <v>-0.03472599433549675</v>
       </c>
       <c r="G18">
-        <v>0.2291866613168793</v>
+        <v>0.252655467404076</v>
       </c>
       <c r="H18">
-        <v>0.29866596613665</v>
+        <v>-0.1374440644102861</v>
       </c>
       <c r="I18">
-        <v>0.7651949274897687</v>
+        <v>0.8906798031518055</v>
       </c>
       <c r="J18">
-        <v>-0.3463067618842783</v>
+        <v>-0.4800063582472885</v>
       </c>
       <c r="K18">
-        <v>0.5126256694814622</v>
+        <v>0.547536180335071</v>
       </c>
       <c r="L18">
-        <v>0.06845025591204912</v>
+        <v>-0.03472599433170231</v>
       </c>
       <c r="M18">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -5718,28 +5718,28 @@
         <v>90</v>
       </c>
       <c r="F19">
-        <v>-0.4593926374991478</v>
+        <v>0.1716548046020226</v>
       </c>
       <c r="G19">
-        <v>0.2511851609401504</v>
+        <v>0.2732474535014829</v>
       </c>
       <c r="H19">
-        <v>-1.828900384798634</v>
+        <v>0.6282027605468282</v>
       </c>
       <c r="I19">
-        <v>0.06741453259358909</v>
+        <v>0.5298711221318164</v>
       </c>
       <c r="J19">
-        <v>-0.9415964524615551</v>
+        <v>-0.3480595377567794</v>
       </c>
       <c r="K19">
-        <v>-0.005657997153639442</v>
+        <v>0.48698397185857</v>
       </c>
       <c r="L19">
-        <v>-0.4593926394065777</v>
+        <v>0.171654804583266</v>
       </c>
       <c r="M19">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5759,28 +5759,28 @@
         <v>94</v>
       </c>
       <c r="F20">
-        <v>-0.07445060330067947</v>
+        <v>-0.0659582408408306</v>
       </c>
       <c r="G20">
-        <v>0.1400952945299878</v>
+        <v>0.16468415690999</v>
       </c>
       <c r="H20">
-        <v>-0.5314282935087665</v>
+        <v>-0.4005135774953801</v>
       </c>
       <c r="I20">
-        <v>0.5951220193407818</v>
+        <v>0.6887782851350015</v>
       </c>
       <c r="J20">
-        <v>-0.3344940547802284</v>
+        <v>-0.4703892443648931</v>
       </c>
       <c r="K20">
-        <v>0.2012415650051572</v>
+        <v>0.1709016518071516</v>
       </c>
       <c r="L20">
-        <v>-0.07445060360980352</v>
+        <v>-0.06595824083362341</v>
       </c>
       <c r="M20">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5800,28 +5800,28 @@
         <v>97</v>
       </c>
       <c r="F21">
-        <v>-0.05703910827479278</v>
+        <v>-0.05648026379316952</v>
       </c>
       <c r="G21">
-        <v>0.1432485558089512</v>
+        <v>0.149635742334569</v>
       </c>
       <c r="H21">
-        <v>-0.3981827806408403</v>
+        <v>-0.3774516897633046</v>
       </c>
       <c r="I21">
-        <v>0.6904954578702571</v>
+        <v>0.7058379597465201</v>
       </c>
       <c r="J21">
-        <v>-0.3286069831118746</v>
+        <v>-0.4086795542680349</v>
       </c>
       <c r="K21">
-        <v>0.207143680061023</v>
+        <v>0.1842377562072706</v>
       </c>
       <c r="L21">
-        <v>-0.0570391085116231</v>
+        <v>-0.05648026378699798</v>
       </c>
       <c r="M21">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5841,28 +5841,28 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>-0.2390080279646725</v>
+        <v>-0.1854096355681109</v>
       </c>
       <c r="G22">
-        <v>0.291618869820331</v>
+        <v>0.2750438193101768</v>
       </c>
       <c r="H22">
-        <v>-0.8195904061761418</v>
+        <v>-0.6741094420268275</v>
       </c>
       <c r="I22">
-        <v>0.4124496446456833</v>
+        <v>0.5002417370504906</v>
       </c>
       <c r="J22">
-        <v>-0.8662020200788551</v>
+        <v>-0.9027297117509715</v>
       </c>
       <c r="K22">
-        <v>0.2855535971785857</v>
+        <v>0.1938446281845205</v>
       </c>
       <c r="L22">
-        <v>-0.2390080289570504</v>
+        <v>-0.1854096355478513</v>
       </c>
       <c r="M22">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5882,28 +5882,28 @@
         <v>103</v>
       </c>
       <c r="F23">
-        <v>0.01741149502588669</v>
+        <v>0.009477977047661075</v>
       </c>
       <c r="G23">
-        <v>0.1082961710085189</v>
+        <v>0.126768778578292</v>
       </c>
       <c r="H23">
-        <v>0.1607766448595587</v>
+        <v>0.07476586233579199</v>
       </c>
       <c r="I23">
-        <v>0.8722693206119361</v>
+        <v>0.9404010036770227</v>
       </c>
       <c r="J23">
-        <v>-0.1671329941102766</v>
+        <v>-0.2147023685369325</v>
       </c>
       <c r="K23">
-        <v>0.2292603598398735</v>
+        <v>0.2985863357940144</v>
       </c>
       <c r="L23">
-        <v>0.01741149509818042</v>
+        <v>0.009477977046625424</v>
       </c>
       <c r="M23">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5923,28 +5923,28 @@
         <v>106</v>
       </c>
       <c r="F24">
-        <v>-0.164557424663993</v>
+        <v>-0.1194513947272803</v>
       </c>
       <c r="G24">
-        <v>0.2352034322843305</v>
+        <v>0.2611493632646583</v>
       </c>
       <c r="H24">
-        <v>-0.6996387045281908</v>
+        <v>-0.4574064176684354</v>
       </c>
       <c r="I24">
-        <v>0.4841529648399217</v>
+        <v>0.6473789523917919</v>
       </c>
       <c r="J24">
-        <v>-0.666753935843804</v>
+        <v>-0.7597605919434829</v>
       </c>
       <c r="K24">
-        <v>0.2267616702994446</v>
+        <v>0.3353433263461005</v>
       </c>
       <c r="L24">
-        <v>-0.1645574253472468</v>
+        <v>-0.1194513947142279</v>
       </c>
       <c r="M24">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5964,28 +5964,28 @@
         <v>109</v>
       </c>
       <c r="F25">
-        <v>-0.1819689196898797</v>
+        <v>-0.1289293717749413</v>
       </c>
       <c r="G25">
-        <v>0.270967869536652</v>
+        <v>0.2783502889965796</v>
       </c>
       <c r="H25">
-        <v>-0.6715516492824106</v>
+        <v>-0.4631910828607964</v>
       </c>
       <c r="I25">
-        <v>0.5018691680603455</v>
+        <v>0.6432274073566069</v>
       </c>
       <c r="J25">
-        <v>-0.8129437837210063</v>
+        <v>-0.8469522670748649</v>
       </c>
       <c r="K25">
-        <v>0.2616109488257513</v>
+        <v>0.2856654408924872</v>
       </c>
       <c r="L25">
-        <v>-0.1819689204454273</v>
+        <v>-0.1289293717608533</v>
       </c>
       <c r="M25">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
